--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo\7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="6195" firstSheet="1" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -26,14 +26,14 @@
     <sheet name="version" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$5</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="273">
   <si>
     <t>idA</t>
   </si>
@@ -92,354 +92,42 @@
     <t>nationality_</t>
   </si>
   <si>
-    <t>Ульянов Владимир Ильич</t>
-  </si>
-  <si>
     <t>М</t>
   </si>
   <si>
-    <t>Ленин</t>
-  </si>
-  <si>
     <t>Ульянов_Илья_Николаевич</t>
   </si>
   <si>
     <t>Бланк_Мария_Александровна</t>
   </si>
   <si>
-    <t>1870</t>
-  </si>
-  <si>
-    <t>10 (22).04 1870</t>
-  </si>
-  <si>
-    <t>1924</t>
-  </si>
-  <si>
-    <t>21.01.1924</t>
-  </si>
-  <si>
     <t>Симбирск</t>
   </si>
   <si>
-    <t>Горки</t>
-  </si>
-  <si>
-    <t>Мавзолей, Москва</t>
-  </si>
-  <si>
-    <t>революционер, политик</t>
-  </si>
-  <si>
-    <t>Ульянов Илья Николаевич</t>
-  </si>
-  <si>
     <t>Ульянин_Николай_Васильевич</t>
   </si>
   <si>
     <t>Смирнова_Анна_Алексеевна</t>
   </si>
   <si>
-    <t>1831</t>
-  </si>
-  <si>
-    <t>1886</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q280722</t>
-  </si>
-  <si>
     <t>Астрахань</t>
   </si>
   <si>
-    <t>педагог, инспектор народных училищ</t>
-  </si>
-  <si>
-    <t>Бланк Мария Александровна</t>
-  </si>
-  <si>
     <t>Ж</t>
   </si>
   <si>
-    <t>Ульянова</t>
-  </si>
-  <si>
     <t>Бланк_Александр_Дмитриевич</t>
   </si>
   <si>
     <t>Гроссшопф_Анна_Ивановна</t>
   </si>
   <si>
-    <t>1835</t>
-  </si>
-  <si>
-    <t>1916</t>
-  </si>
-  <si>
-    <t>https://ru.ruwiki.ru/wiki/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D0%B0,_%D0%9C%D0%B0%D1%80%D0%B8%D1%8F_%D0%90%D0%BB%D0%B5%D0%BA%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%BE%D0%B2%D0%BD%D0%B0 ; https://ru.wikipedia.org/wiki/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D0%B0,_%D0%9C%D0%B0%D1%80%D0%B8%D1%8F_%D0%90%D0%BB%D0%B5%D0%BA%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%BE%D0%B2%D0%BD%D0%B0 ; https://www.wikidata.org/wiki/Q470041</t>
-  </si>
-  <si>
-    <t>Санкт-Петербург</t>
-  </si>
-  <si>
-    <t>Петроград</t>
-  </si>
-  <si>
-    <t>учительница</t>
-  </si>
-  <si>
-    <t>Ульянин Николай Васильевич</t>
-  </si>
-  <si>
-    <t>1768</t>
-  </si>
-  <si>
-    <t>1836</t>
-  </si>
-  <si>
-    <t>Нижегородская губерния</t>
-  </si>
-  <si>
-    <t>портной, мещанин</t>
-  </si>
-  <si>
-    <t>Смирнова Анна Алексеевна</t>
-  </si>
-  <si>
-    <t>1788</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>домохозяйка</t>
-  </si>
-  <si>
-    <t>Бланк Александр Дмитриевич</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>Староконстантинов</t>
-  </si>
-  <si>
-    <t>Кокушкино</t>
-  </si>
-  <si>
-    <t>врач</t>
-  </si>
-  <si>
-    <t>Гроссшопф Анна Ивановна</t>
-  </si>
-  <si>
-    <t>1799</t>
-  </si>
-  <si>
-    <t>1838</t>
-  </si>
-  <si>
-    <t>Любек, Германия</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
-    <t>Ульянова Анна Ильинична</t>
-  </si>
-  <si>
-    <t>Елизарова</t>
-  </si>
-  <si>
-    <t>1864</t>
-  </si>
-  <si>
-    <t>14.08.1864</t>
-  </si>
-  <si>
-    <t>1935</t>
-  </si>
-  <si>
-    <t>19.10.1935</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q4174883</t>
-  </si>
-  <si>
-    <t>Ульянов Александр Ильич</t>
-  </si>
-  <si>
-    <t>1866</t>
-  </si>
-  <si>
-    <t>12.04.1866</t>
-  </si>
-  <si>
-    <t>1887</t>
-  </si>
-  <si>
-    <t>20.05.1887</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q333241</t>
-  </si>
-  <si>
-    <t>Ульянова Ольга Ильинична</t>
-  </si>
-  <si>
-    <t>1891</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q4475081</t>
-  </si>
-  <si>
-    <t>Ульянов Дмитрий Ильич</t>
-  </si>
-  <si>
-    <t>1874</t>
-  </si>
-  <si>
-    <t>1943</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q1965609</t>
-  </si>
-  <si>
-    <t>Ульянова Мария Ильинична</t>
-  </si>
-  <si>
-    <t>1878</t>
-  </si>
-  <si>
-    <t>18.02.1878</t>
-  </si>
-  <si>
-    <t>1937</t>
-  </si>
-  <si>
-    <t>12.06.1937</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q4475079</t>
-  </si>
-  <si>
-    <t>Крупская Надежда Константиновна</t>
-  </si>
-  <si>
-    <t>1869</t>
-  </si>
-  <si>
-    <t>14.02.1869</t>
-  </si>
-  <si>
-    <t>1939</t>
-  </si>
-  <si>
-    <t>27.02.1939</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q215637</t>
-  </si>
-  <si>
-    <t>Ульянов Василий Николаевич</t>
-  </si>
-  <si>
-    <t>1823</t>
-  </si>
-  <si>
     <t>~1823</t>
   </si>
   <si>
-    <t>~1878</t>
-  </si>
-  <si>
-    <t>приказчик (управляющий соляным делом)</t>
-  </si>
-  <si>
-    <t>Ульянова Мария Николаевна</t>
-  </si>
-  <si>
-    <t>Горшкова</t>
-  </si>
-  <si>
-    <t>~1825</t>
-  </si>
-  <si>
-    <t>Ульянова Феодосия Николаевна</t>
-  </si>
-  <si>
-    <t>~1827</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>Бланк Дмитрий Александрович</t>
-  </si>
-  <si>
-    <t>1830</t>
-  </si>
-  <si>
-    <t>09.09.1830</t>
-  </si>
-  <si>
-    <t>1850</t>
-  </si>
-  <si>
-    <t>19.01.1850</t>
-  </si>
-  <si>
-    <t>Российская Империя</t>
-  </si>
-  <si>
-    <t>Казань</t>
-  </si>
-  <si>
-    <t>студент юридического факультета</t>
-  </si>
-  <si>
-    <t>Бланк Анна Александровна</t>
-  </si>
-  <si>
-    <t>Веретенникова</t>
-  </si>
-  <si>
-    <t>30.08.1831</t>
-  </si>
-  <si>
-    <t>Бланк Любовь Александровна</t>
-  </si>
-  <si>
-    <t>Ардашева/Пономарёва</t>
-  </si>
-  <si>
-    <t>1832</t>
-  </si>
-  <si>
-    <t>29.08.1832</t>
-  </si>
-  <si>
-    <t>Бланк Екатерина Александровна</t>
-  </si>
-  <si>
-    <t>Залежская</t>
-  </si>
-  <si>
-    <t>1834</t>
-  </si>
-  <si>
-    <t>04.01.1834</t>
-  </si>
-  <si>
-    <t>Бланк Софья Александровна</t>
-  </si>
-  <si>
-    <t>Лаврова</t>
-  </si>
-  <si>
-    <t>24.07.1836</t>
-  </si>
-  <si>
     <t>husband</t>
   </si>
   <si>
@@ -1064,18 +752,6 @@
     <t>Перевод на английский</t>
   </si>
   <si>
-    <t>17.07.1870</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q29474575 ; https://ru.wikipedia.org/wiki/%D0%A1%D0%B5%D0%BC%D1%8C%D1%8F_%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2%D1%8B%D1%85#%D0%9C%D0%B0%D1%82%D0%B5%D1%80%D0%B8%D0%BD%D1%81%D0%BA%D0%B0%D1%8F_%D0%BB%D0%B8%D0%BD%D0%B8%D1%8F</t>
-  </si>
-  <si>
-    <t>Эссен Екатерина Ивановна</t>
-  </si>
-  <si>
-    <t>https://www.famhist.ru/famhist/lenin_b/0003cac9.htm</t>
-  </si>
-  <si>
     <t>Эссен_Екатерина_Ивановна</t>
   </si>
   <si>
@@ -1118,12 +794,6 @@
     <t>музей</t>
   </si>
   <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%9B%D0%B5%D0%BD%D0%B8%D0%BD,_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87 ; https://www.wikidata.org/wiki/Q1394 ; https://github.com/bpmbpm/family-tree/blob/main/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md ; https://bpmbpm.github.io/family-tree/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md</t>
-  </si>
-  <si>
-    <t>./md_person/Ульянин_Николай_Васильевич.md ; ./md_person/Ульянин_Николай_Васильевич.pdf</t>
-  </si>
-  <si>
     <t>foto_item</t>
   </si>
   <si>
@@ -1137,6 +807,51 @@
   </si>
   <si>
     <t>v_0.01</t>
+  </si>
+  <si>
+    <t>Кононов Андрей Николаевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кононова </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.11.1893 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1893 </t>
+  </si>
+  <si>
+    <t>29.08.1984</t>
+  </si>
+  <si>
+    <t>1984</t>
+  </si>
+  <si>
+    <t>~1941</t>
+  </si>
+  <si>
+    <t>~1893</t>
+  </si>
+  <si>
+    <t>Кононова Анна Андреевна</t>
+  </si>
+  <si>
+    <t>Кононова Клавдия Андреевна</t>
+  </si>
+  <si>
+    <t>Кононова Александра Андреевна</t>
+  </si>
+  <si>
+    <t>Кононов Николай Андреевич</t>
+  </si>
+  <si>
+    <t>Обозова_Прасковья_Михайловна</t>
+  </si>
+  <si>
+    <t>Обозова Прасковья Михайловна</t>
+  </si>
+  <si>
+    <t>Кононов_Андрей_Николаевич</t>
   </si>
 </sst>
 </file>
@@ -1220,11 +935,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1522,22 +1235,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="31" style="7" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="7" customWidth="1"/>
-    <col min="9" max="10" width="15.28515625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="16" style="7" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" style="7" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="32.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="31" style="5" customWidth="1"/>
+    <col min="6" max="6" width="33.5703125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="5" customWidth="1"/>
+    <col min="9" max="10" width="15.28515625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="16" style="5" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" style="5" customWidth="1"/>
     <col min="15" max="15" width="18.5703125" customWidth="1"/>
     <col min="16" max="16" width="13.7109375" customWidth="1"/>
     <col min="17" max="17" width="14.28515625" customWidth="1"/>
@@ -1603,787 +1316,146 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:A23" si="0">SUBSTITUTE(B2, " ", "_")</f>
-        <v>Ульянов_Владимир_Ильич</v>
-      </c>
-      <c r="B2" s="4" t="s">
+        <f t="shared" ref="A2:A7" si="0">SUBSTITUTE(B2, " ", "_")</f>
+        <v>Кононов_Андрей_Николаевич</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+    </row>
+    <row r="3" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f t="shared" si="0"/>
-        <v>Ульянов_Илья_Николаевич</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>Обозова_Прасковья_Михайловна</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="R3"/>
+    </row>
+    <row r="4" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <f t="shared" si="0"/>
-        <v>Бланк_Мария_Александровна</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>43</v>
+        <f>SUBSTITUTE(B4, " ", "_")</f>
+        <v>Кононова_Анна_Андреевна</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>272</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="O4" t="s">
-        <v>48</v>
-      </c>
-      <c r="P4" t="s">
-        <v>49</v>
-      </c>
-      <c r="R4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="R4"/>
+    </row>
+    <row r="5" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
-        <v>Ульянин_Николай_Васильевич</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="G5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="O5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
+        <v>Кононова_Клавдия_Андреевна</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="R5"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Смирнова_Анна_Алексеевна</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" t="s">
-        <v>38</v>
-      </c>
-      <c r="P6" t="s">
-        <v>38</v>
-      </c>
-      <c r="R6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
+        <v>Кононова_Александра_Андреевна</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Бланк_Александр_Дмитриевич</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" t="s">
-        <v>343</v>
-      </c>
-      <c r="K7" t="s">
-        <v>344</v>
-      </c>
-      <c r="O7" t="s">
-        <v>62</v>
-      </c>
-      <c r="P7" t="s">
-        <v>63</v>
-      </c>
-      <c r="R7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
-        <f t="shared" si="0"/>
-        <v>Гроссшопф_Анна_Ивановна</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" t="s">
-        <v>67</v>
-      </c>
-      <c r="J8" t="s">
-        <v>67</v>
-      </c>
-      <c r="O8" t="s">
-        <v>68</v>
-      </c>
-      <c r="P8" t="s">
-        <v>69</v>
-      </c>
-      <c r="R8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянова_Анна_Ильинична</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянов_Александр_Ильич</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J10" t="s">
-        <v>81</v>
-      </c>
-      <c r="K10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянова_Ольга_Ильинична</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянов_Дмитрий_Ильич</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" t="s">
-        <v>88</v>
-      </c>
-      <c r="K12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянова_Мария_Ильинична</v>
-      </c>
-      <c r="B13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" t="s">
-        <v>94</v>
-      </c>
-      <c r="K13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" t="str">
-        <f t="shared" si="0"/>
-        <v>Крупская_Надежда_Константиновна</v>
-      </c>
-      <c r="B14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I14" t="s">
-        <v>99</v>
-      </c>
-      <c r="J14" t="s">
-        <v>100</v>
-      </c>
-      <c r="K14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянов_Василий_Николаевич</v>
-      </c>
-      <c r="B15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" t="s">
-        <v>105</v>
-      </c>
-      <c r="J15" t="s">
-        <v>105</v>
-      </c>
-      <c r="R15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянова_Мария_Николаевна</v>
-      </c>
-      <c r="B16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" t="s">
-        <v>109</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="I16" t="s">
-        <v>69</v>
-      </c>
-      <c r="J16" t="s">
-        <v>69</v>
-      </c>
-      <c r="R16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянова_Феодосия_Николаевна</v>
-      </c>
-      <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I17" t="s">
-        <v>112</v>
-      </c>
-      <c r="J17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Бланк_Дмитрий_Александрович</v>
-      </c>
-      <c r="B18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" t="s">
-        <v>114</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="I18" t="s">
-        <v>116</v>
-      </c>
-      <c r="J18" t="s">
-        <v>117</v>
-      </c>
-      <c r="O18" t="s">
-        <v>118</v>
-      </c>
-      <c r="P18" t="s">
-        <v>119</v>
-      </c>
-      <c r="R18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Бланк_Анна_Александровна</v>
-      </c>
-      <c r="B19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="I19" t="s">
-        <v>69</v>
-      </c>
-      <c r="J19" t="s">
-        <v>69</v>
-      </c>
-      <c r="R19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Бланк_Любовь_Александровна</v>
-      </c>
-      <c r="B20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" t="s">
-        <v>125</v>
-      </c>
-      <c r="E20" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" t="s">
-        <v>126</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I20" t="s">
-        <v>69</v>
-      </c>
-      <c r="J20" t="s">
-        <v>69</v>
-      </c>
-      <c r="R20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Бланк_Екатерина_Александровна</v>
-      </c>
-      <c r="B21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C21" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" t="s">
-        <v>130</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="I21" t="s">
-        <v>69</v>
-      </c>
-      <c r="J21" t="s">
-        <v>69</v>
-      </c>
-      <c r="R21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Бланк_Софья_Александровна</v>
-      </c>
-      <c r="B22" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" t="s">
-        <v>133</v>
-      </c>
-      <c r="E22" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" t="s">
-        <v>69</v>
-      </c>
-      <c r="J22" t="s">
-        <v>69</v>
-      </c>
-      <c r="R22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>Эссен_Екатерина_Ивановна</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I23" s="4">
-        <v>1863</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>346</v>
+        <v>Кононов_Николай_Андреевич</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N22"/>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F9">
+  <autoFilter ref="A1:N5"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F5">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" tooltip="Ульянова, Мария Александровна"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2392,28 +1464,28 @@
   <dimension ref="A1:L48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>210</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>211</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>212</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2425,801 +1497,801 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>218</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>219</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>222</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>223</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>225</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>227</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>231</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>232</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
-        <v>236</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>231</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>232</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>225</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>236</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B19" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>231</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>232</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>225</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B21" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B22" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="E22" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>236</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>231</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
-        <v>232</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B25" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
-        <v>225</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="D26" t="s">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="E26" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B27" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>236</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>231</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
-        <v>232</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
-        <v>225</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>237</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s">
-        <v>238</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="E32" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B33" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="C34" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="E34" t="s">
-        <v>236</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>231</v>
+        <v>127</v>
       </c>
       <c r="E35" t="s">
-        <v>232</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B36" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="E36" t="s">
-        <v>225</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B37" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="D38" t="s">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="E38" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>241</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s">
-        <v>242</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>243</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>244</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>245</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>246</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>247</v>
+        <v>143</v>
       </c>
       <c r="E42" t="s">
-        <v>248</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="D43" t="s">
-        <v>355</v>
+        <v>247</v>
       </c>
       <c r="E43" t="s">
-        <v>249</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B44" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="D44" t="s">
-        <v>250</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
-        <v>251</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>214</v>
+      <c r="A45" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B45" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>252</v>
+        <v>148</v>
       </c>
       <c r="E45" t="s">
-        <v>253</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>214</v>
+      <c r="A46" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B46" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="C46" t="s">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="D46" t="s">
-        <v>254</v>
+        <v>150</v>
       </c>
       <c r="E46" t="s">
-        <v>255</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>135</v>
+      <c r="A47" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>136</v>
+      <c r="A48" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3233,1162 +2305,1162 @@
   <dimension ref="A1:C107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20" style="7" customWidth="1"/>
-    <col min="3" max="3" width="60" style="7" customWidth="1"/>
+    <col min="1" max="2" width="20" style="5" customWidth="1"/>
+    <col min="3" max="3" width="60" style="5" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>258</v>
+      <c r="A1" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>259</v>
+        <v>111</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>260</v>
+      <c r="C3" s="9" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>261</v>
+      <c r="C4" s="9" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>262</v>
+      <c r="C5" s="9" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>263</v>
+      <c r="C6" s="9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>264</v>
+      <c r="C7" s="9" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>265</v>
+      <c r="C8" s="9" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>266</v>
+      <c r="C9" s="9" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>267</v>
+      <c r="C10" s="9" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>268</v>
+      <c r="C11" s="9" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>269</v>
+      <c r="C12" s="9" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>270</v>
+      <c r="C13" s="9" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>271</v>
+      <c r="C14" s="9" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>272</v>
+      <c r="C15" s="9" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>273</v>
+      <c r="C16" s="9" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>274</v>
+      <c r="C17" s="9" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>275</v>
+      <c r="C18" s="9" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>276</v>
+      <c r="C19" s="9" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>277</v>
+      <c r="C20" s="9" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>252</v>
+      <c r="C21" s="9" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>226</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>278</v>
+        <v>122</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>279</v>
+      <c r="C23" s="9" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>280</v>
+        <v>31</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>281</v>
+        <v>32</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>282</v>
+        <v>33</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>283</v>
+        <v>39</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B28" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>284</v>
+        <v>34</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>285</v>
+        <v>35</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>286</v>
+        <v>36</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11" t="s">
-        <v>287</v>
+      <c r="C31" s="9" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>270</v>
+      <c r="C32" s="9" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B33" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>288</v>
+        <v>37</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>289</v>
+        <v>38</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>196</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>290</v>
+        <v>92</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>291</v>
+        <v>51</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>292</v>
+        <v>52</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>293</v>
+        <v>53</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="11" t="s">
-        <v>294</v>
+      <c r="C39" s="9" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>158</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>295</v>
+        <v>54</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>296</v>
+        <v>55</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>160</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>297</v>
+        <v>56</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="11" t="s">
-        <v>298</v>
+      <c r="C43" s="9" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="11" t="s">
-        <v>299</v>
+      <c r="C44" s="9" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>197</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>300</v>
+        <v>93</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="B46" t="s">
-        <v>165</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>166</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>292</v>
+        <v>62</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>157</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>302</v>
+        <v>53</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B49" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>303</v>
+      <c r="C49" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>304</v>
+        <v>54</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s">
-        <v>167</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>305</v>
+        <v>63</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B52" t="s">
-        <v>168</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>306</v>
+        <v>64</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B53" t="s">
-        <v>169</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>307</v>
+        <v>65</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>159</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>296</v>
+        <v>55</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>297</v>
+        <v>56</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
-        <v>170</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>308</v>
+        <v>66</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="11" t="s">
-        <v>298</v>
+      <c r="C57" s="9" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="11" t="s">
-        <v>309</v>
+      <c r="C58" s="9" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>310</v>
+        <v>67</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>198</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>311</v>
+        <v>94</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B61" t="s">
-        <v>155</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>312</v>
+        <v>51</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B62" t="s">
-        <v>166</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>313</v>
+        <v>62</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="B63" t="s">
-        <v>157</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B64" t="s">
         <v>0</v>
       </c>
-      <c r="C64" s="11" t="s">
-        <v>303</v>
+      <c r="C64" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B65" t="s">
-        <v>158</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>304</v>
+        <v>54</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>310</v>
+        <v>67</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>296</v>
+        <v>55</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>297</v>
+        <v>56</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B69" t="s">
-        <v>170</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>308</v>
+        <v>66</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="11" t="s">
-        <v>298</v>
+      <c r="C70" s="9" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="B71" t="s">
         <v>10</v>
       </c>
-      <c r="C71" s="11" t="s">
-        <v>309</v>
+      <c r="C71" s="9" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>199</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>314</v>
+        <v>95</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B73" t="s">
-        <v>185</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>315</v>
+        <v>81</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B74" t="s">
-        <v>156</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>313</v>
+        <v>52</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B75" t="s">
-        <v>157</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>302</v>
+        <v>53</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B76" t="s">
         <v>0</v>
       </c>
-      <c r="C76" s="11" t="s">
-        <v>303</v>
+      <c r="C76" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B77" t="s">
-        <v>158</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>316</v>
+        <v>54</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B78" t="s">
-        <v>186</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>317</v>
+        <v>82</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>318</v>
+        <v>67</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B80" t="s">
-        <v>187</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>319</v>
+        <v>83</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>159</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>320</v>
+        <v>55</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B82" t="s">
-        <v>160</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>297</v>
+        <v>56</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>308</v>
+        <v>66</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B84" t="s">
         <v>1</v>
       </c>
-      <c r="C84" s="11" t="s">
-        <v>298</v>
+      <c r="C84" s="9" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
       </c>
-      <c r="C85" s="11" t="s">
-        <v>309</v>
+      <c r="C85" s="9" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="B86" t="s">
-        <v>188</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>321</v>
+        <v>84</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>239</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>322</v>
+        <v>135</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B88" t="s">
-        <v>194</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>323</v>
+        <v>90</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B89" t="s">
-        <v>195</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>324</v>
+        <v>91</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B90" t="s">
-        <v>171</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>325</v>
+        <v>67</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B91" t="s">
-        <v>187</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>319</v>
+        <v>83</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B92" t="s">
-        <v>158</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>326</v>
+        <v>54</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B93" t="s">
-        <v>159</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>327</v>
+        <v>55</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B94" t="s">
-        <v>160</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>328</v>
+        <v>56</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>329</v>
+        <v>66</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B96" t="s">
         <v>1</v>
       </c>
-      <c r="C96" s="11" t="s">
-        <v>330</v>
+      <c r="C96" s="9" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="11" t="s">
-        <v>331</v>
+      <c r="C97" s="9" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B98" t="s">
-        <v>196</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>332</v>
+        <v>92</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>197</v>
-      </c>
-      <c r="C99" s="11" t="s">
-        <v>333</v>
+        <v>93</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>198</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>334</v>
+        <v>94</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="B101" t="s">
-        <v>199</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>335</v>
+        <v>95</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>336</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>337</v>
+        <v>232</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="B103" t="s">
-        <v>209</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>338</v>
+        <v>105</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="B104" t="s">
-        <v>210</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>339</v>
+        <v>106</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>340</v>
+        <v>107</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>341</v>
+        <v>108</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="B107" t="s">
-        <v>213</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>342</v>
+        <v>109</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -4407,15 +3479,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>367</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4429,14 +3501,14 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.42578125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="43.5703125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="30" style="7" customWidth="1"/>
-    <col min="5" max="5" width="12" style="7" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="11" style="7" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="59.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="39.5703125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="30" style="5" customWidth="1"/>
+    <col min="5" max="5" width="12" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11" style="5" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -4444,22 +3516,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -4468,13 +3540,13 @@
         <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="M1" s="1"/>
     </row>
@@ -4483,107 +3555,107 @@
         <f>B2&amp;"__"&amp;C2</f>
         <v>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>22</v>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="K2" t="s">
-        <v>146</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="str">
+      <c r="A3" s="5" t="str">
         <f t="shared" ref="A3:A6" si="0">B3&amp;"__"&amp;C3</f>
         <v>Бланк_Александр_Дмитриевич__Гроссшопф_Анна_Ивановна</v>
       </c>
       <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
         <v>43</v>
       </c>
-      <c r="C3" t="s">
+      <c r="K3" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" t="s">
-        <v>147</v>
-      </c>
-      <c r="K3" t="s">
-        <v>148</v>
-      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="str">
+      <c r="A4" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Ульянов_Владимир_Ильич__Крупская_Надежда_Константиновна</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="K4" t="s">
-        <v>146</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Ульянин_Николай_Васильевич__Смирнова_Анна_Алексеевна</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>146</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="str">
+      <c r="A6" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Бланк_Александр_Дмитриевич__Эссен_Екатерина_Ивановна</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>349</v>
+      <c r="B6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -4602,44 +3674,44 @@
   <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="43.42578125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="7" customWidth="1"/>
-    <col min="12" max="13" width="16" style="7" customWidth="1"/>
-    <col min="14" max="14" width="26.140625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="43.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="5" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" style="5" customWidth="1"/>
+    <col min="12" max="13" width="16" style="5" customWidth="1"/>
+    <col min="14" max="14" width="26.140625" style="5" customWidth="1"/>
     <col min="15" max="15" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>170</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -4648,127 +3720,127 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>196</v>
+        <v>92</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="P1" s="13" t="s">
-        <v>364</v>
+        <v>95</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>178</v>
+        <v>97</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="K2" t="s">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="M2" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>205</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>206</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="F3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G3" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="G3" s="2"/>
       <c r="M3" t="s">
-        <v>207</v>
+        <v>103</v>
       </c>
       <c r="N3" t="s">
-        <v>208</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G4" s="4"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G5" s="4"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G6" s="4"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G7" s="4"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G8" s="4"/>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G9" s="4"/>
+      <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G10" s="4"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G11" s="4"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G12" s="4"/>
+      <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G13" s="4"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G14" s="4"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G15" s="4"/>
+      <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G16" s="4"/>
+      <c r="G16" s="2"/>
     </row>
     <row r="17" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G17" s="4"/>
+      <c r="G17" s="2"/>
     </row>
     <row r="18" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G18" s="4"/>
+      <c r="G18" s="2"/>
     </row>
     <row r="19" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G19" s="4"/>
+      <c r="G19" s="2"/>
     </row>
     <row r="20" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G20" s="4"/>
+      <c r="G20" s="2"/>
     </row>
     <row r="21" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G21" s="4"/>
+      <c r="G21" s="2"/>
     </row>
     <row r="22" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G22" s="4"/>
+      <c r="G22" s="2"/>
     </row>
     <row r="23" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G23" s="4"/>
+      <c r="G23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4781,41 +3853,41 @@
   <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="15" style="7" customWidth="1"/>
-    <col min="4" max="5" width="34.7109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="11" style="7" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21" style="7" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15" style="5" customWidth="1"/>
+    <col min="4" max="5" width="34.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" style="5" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -4826,100 +3898,100 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="B2">
         <v>1922</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>57</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1922.jpg</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>149</v>
+      <c r="E2" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>163</v>
+        <v>58</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="J2" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H3" s="4"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H4" s="4"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G5" s="6"/>
-      <c r="H5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H6" s="4"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H7" s="4"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H8" s="4"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H9" s="4"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H10" s="4"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H11" s="4"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H12" s="4"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H13" s="4"/>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H14" s="4"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H15" s="4"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H16" s="4"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H17" s="4"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H18" s="4"/>
+      <c r="H18" s="2"/>
     </row>
     <row r="19" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H19" s="4"/>
+      <c r="H19" s="2"/>
     </row>
     <row r="20" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H20" s="4"/>
+      <c r="H20" s="2"/>
     </row>
     <row r="21" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H21" s="4"/>
+      <c r="H21" s="2"/>
     </row>
     <row r="22" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H22" s="4"/>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H23" s="4"/>
+      <c r="H23" s="2"/>
     </row>
     <row r="24" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H24" s="4"/>
+      <c r="H24" s="2"/>
     </row>
     <row r="25" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H25" s="4"/>
+      <c r="H25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4932,54 +4004,54 @@
   <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="15" style="7" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="62.85546875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="5.85546875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="7" customWidth="1"/>
-    <col min="9" max="10" width="14.140625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="32.140625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="30.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" style="7" customWidth="1"/>
-    <col min="14" max="14" width="17" style="7" customWidth="1"/>
+    <col min="1" max="1" width="55.140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="62.85546875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="5" customWidth="1"/>
+    <col min="9" max="10" width="14.140625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="32.140625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="30.42578125" style="5" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="17" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>66</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4988,99 +4060,99 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>350</v>
+        <v>242</v>
       </c>
       <c r="B2">
         <v>1879</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>57</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна-1879.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="4">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2">
         <v>1879</v>
       </c>
       <c r="L2" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="M2" t="s">
-        <v>175</v>
+        <v>71</v>
       </c>
       <c r="N2" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J3" s="4"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J4" s="4"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J5" s="4"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J6" s="4"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="5"/>
-      <c r="J7" s="4"/>
+      <c r="E7" s="3"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J8" s="4"/>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J9" s="4"/>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J10" s="4"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J11" s="4"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J12" s="4"/>
+      <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J13" s="4"/>
+      <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J14" s="4"/>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J15" s="4"/>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J16" s="4"/>
+      <c r="J16" s="2"/>
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J17" s="4"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J18" s="4"/>
+      <c r="J18" s="2"/>
     </row>
     <row r="19" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J19" s="4"/>
+      <c r="J19" s="2"/>
     </row>
     <row r="20" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J20" s="4"/>
+      <c r="J20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5104,39 +4176,39 @@
     <col min="13" max="13" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>66</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -5145,38 +4217,38 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D2" s="7" t="str">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>календарь-вещи.png</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="7" t="s">
-        <v>356</v>
+      <c r="E2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="M2" s="5" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -5189,44 +4261,44 @@
   <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="36.42578125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="54" style="7" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="7" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" style="7" customWidth="1"/>
-    <col min="10" max="10" width="32.85546875" style="7" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="54" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="32.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>1</v>
@@ -5235,128 +4307,128 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="B2">
         <v>1918</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>57</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1918.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>178</v>
+        <v>73</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="J2" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="K2" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>180</v>
+      <c r="A3" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="B3">
         <v>1918</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>57</v>
       </c>
       <c r="D3" t="str">
         <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
         <v>Свердлов_Яков_Михайлович-1918.jpg</v>
       </c>
       <c r="E3" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>178</v>
+        <v>79</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="J3" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="K3" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H4" s="4"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H5" s="4"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H6" s="4"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H7" s="4"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H8" s="4"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H9" s="4"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H10" s="4"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="4"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H12" s="4"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H13" s="4"/>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H14" s="4"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H15" s="4"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H16" s="4"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H17" s="4"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H18" s="4"/>
+      <c r="H18" s="2"/>
     </row>
     <row r="19" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H19" s="4"/>
+      <c r="H19" s="2"/>
     </row>
     <row r="20" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H20" s="4"/>
+      <c r="H20" s="2"/>
     </row>
     <row r="21" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H21" s="4"/>
+      <c r="H21" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5372,53 +4444,53 @@
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="34.42578125" style="7" customWidth="1"/>
-    <col min="5" max="6" width="25" style="7" customWidth="1"/>
-    <col min="7" max="7" width="39.28515625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="47.140625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="20.28515625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="16" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" style="7" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="34.42578125" style="5" customWidth="1"/>
+    <col min="5" max="6" width="25" style="5" customWidth="1"/>
+    <col min="7" max="7" width="39.28515625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="47.140625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="16" style="5" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>66</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -5427,44 +4499,44 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>87</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульяновск_ Ленина_70-2020хх.png</v>
       </c>
       <c r="E2" t="s">
-        <v>192</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>193</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>192</v>
-      </c>
-      <c r="L2" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="L2" s="7"/>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -5492,39 +4564,39 @@
     <col min="13" max="13" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>249</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>66</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -5533,38 +4605,38 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D2" s="7" t="str">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>календарь-вещи.png</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="7" t="s">
-        <v>356</v>
+      <c r="E2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="M2" s="5" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="254">
   <si>
     <t>idA</t>
   </si>
@@ -95,39 +95,15 @@
     <t>М</t>
   </si>
   <si>
-    <t>Ульянов_Илья_Николаевич</t>
-  </si>
-  <si>
-    <t>Бланк_Мария_Александровна</t>
-  </si>
-  <si>
     <t>Симбирск</t>
   </si>
   <si>
-    <t>Ульянин_Николай_Васильевич</t>
-  </si>
-  <si>
-    <t>Смирнова_Анна_Алексеевна</t>
-  </si>
-  <si>
-    <t>Астрахань</t>
-  </si>
-  <si>
     <t>Ж</t>
   </si>
   <si>
-    <t>Бланк_Александр_Дмитриевич</t>
-  </si>
-  <si>
-    <t>Гроссшопф_Анна_Ивановна</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
-    <t>~1823</t>
-  </si>
-  <si>
     <t>husband</t>
   </si>
   <si>
@@ -155,39 +131,15 @@
     <t>marriagePlace_</t>
   </si>
   <si>
-    <t>25.08 (6.09) 1863 </t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
     <t>смерть супруга</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>смерть супруги</t>
-  </si>
-  <si>
     <t>Ульянов_Владимир_Ильич</t>
   </si>
   <si>
-    <t>Крупская_Надежда_Константиновна</t>
-  </si>
-  <si>
-    <t>22.07.1898</t>
-  </si>
-  <si>
-    <t>Шушенское</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>id_person</t>
   </si>
   <si>
@@ -750,15 +702,6 @@
   </si>
   <si>
     <t>Перевод на английский</t>
-  </si>
-  <si>
-    <t>Эссен_Екатерина_Ивановна</t>
-  </si>
-  <si>
-    <t>10.04.1841 </t>
-  </si>
-  <si>
-    <t>https://proza.ru/2025/03/17/154 ; https://zwiahel.ucoz.ru/novograd/evrei/lenin_01.html</t>
   </si>
   <si>
     <t>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна</t>
@@ -1322,16 +1265,16 @@
         <v>Кононов_Андрей_Николаевич</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="O2"/>
       <c r="P2"/>
@@ -1344,25 +1287,25 @@
         <v>Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="K3"/>
       <c r="O3"/>
@@ -1375,16 +1318,16 @@
         <v>Кононова_Анна_Андреевна</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="F4" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="O4"/>
       <c r="P4"/>
@@ -1396,16 +1339,16 @@
         <v>Кононова_Клавдия_Андреевна</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="O5"/>
       <c r="P5"/>
@@ -1417,16 +1360,16 @@
         <v>Кононова_Александра_Андреевна</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -1435,16 +1378,16 @@
         <v>Кононов_Николай_Андреевич</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -1473,19 +1416,19 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1497,801 +1440,801 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" t="s">
         <v>110</v>
-      </c>
-      <c r="B8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
         <v>110</v>
-      </c>
-      <c r="B12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" t="s">
         <v>110</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E19" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E21" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
         <v>110</v>
-      </c>
-      <c r="B22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" t="s">
         <v>110</v>
-      </c>
-      <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="E31" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s">
         <v>110</v>
-      </c>
-      <c r="B33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C33" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" t="s">
-        <v>125</v>
-      </c>
-      <c r="E33" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E36" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E38" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E39" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="E40" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="E41" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="E42" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="E43" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E44" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="E45" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="E46" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2312,1155 +2255,1155 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
         <v>0</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B49" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B61" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B64" t="s">
         <v>0</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B67" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B71" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B76" t="s">
         <v>0</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B84" t="s">
         <v>1</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B88" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B89" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B90" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B91" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B92" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B93" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B95" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B96" t="s">
         <v>1</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B100" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B104" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B105" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B106" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B107" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3479,15 +3422,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3498,7 +3441,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.42578125" style="5" customWidth="1"/>
@@ -3509,6 +3452,7 @@
     <col min="7" max="7" width="13.28515625" style="5" customWidth="1"/>
     <col min="8" max="8" width="11" style="5" customWidth="1"/>
     <col min="9" max="9" width="13.140625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -3516,22 +3460,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -3540,123 +3484,52 @@
         <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>B2&amp;"__"&amp;C2</f>
-        <v>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна</v>
+        <v>Кононов_Андрей_Николаевич__Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>253</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="str">
-        <f t="shared" ref="A3:A6" si="0">B3&amp;"__"&amp;C3</f>
-        <v>Бланк_Александр_Дмитриевич__Гроссшопф_Анна_Ивановна</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
+      <c r="B3"/>
+      <c r="C3"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянов_Владимир_Ильич__Крупская_Надежда_Константиновна</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" t="s">
-        <v>42</v>
-      </c>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Ульянин_Николай_Васильевич__Смирнова_Анна_Алексеевна</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Бланк_Александр_Дмитриевич__Эссен_Екатерина_Ивановна</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>241</v>
-      </c>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3690,28 +3563,28 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -3720,66 +3593,66 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K2" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="M2" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="G3" s="2"/>
       <c r="M3" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="N3" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -3866,28 +3739,28 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -3898,29 +3771,29 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>1922</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1922.jpg</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="J2" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -4021,37 +3894,37 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4060,43 +3933,43 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="B2">
         <v>1879</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна-1879.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J2" s="2">
         <v>1879</v>
       </c>
       <c r="L2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -4178,37 +4051,37 @@
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4217,38 +4090,38 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>календарь-вещи.png</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L2" s="7"/>
       <c r="M2" s="5" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -4274,31 +4147,31 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>1</v>
@@ -4307,73 +4180,73 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>1918</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1918.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="J2" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="K2" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B3">
         <v>1918</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D3" t="str">
         <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
         <v>Свердлов_Яков_Михайлович-1918.jpg</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="J3" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="K3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -4460,37 +4333,37 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4499,44 +4372,44 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульяновск_ Ленина_70-2020хх.png</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="I2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="L2" s="7"/>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4566,37 +4439,37 @@
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4605,38 +4478,38 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>календарь-вещи.png</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L2" s="7"/>
       <c r="M2" s="5" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="254">
   <si>
     <t>idA</t>
   </si>
@@ -212,24 +212,6 @@
     <t>7.11.2018</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ленин и Свердлов на Красной площади, во время открытия временного памятника Карлу Марксу</t>
-  </si>
-  <si>
-    <t>Свердлов_Яков_Михайлович</t>
-  </si>
-  <si>
-    <t>Панно «Павшим в борьбе за мир и братство народов».</t>
-  </si>
-  <si>
-    <t>Свердлов_Яков_Михайлович; Ульянов_Владимир_Ильич</t>
-  </si>
-  <si>
-    <t>Москва</t>
-  </si>
-  <si>
-    <t>В.И. Ленин, Я.М. Свердлов, В.А. Аванесов, Н.И. Подвойский, Г.И. Окулова и М.Ф. Владимирский перед открытой мемориальной доской в память павших за мир и братство народов. Панно «Павшим в борьбе за мир и братство народов». Скульптор Сергей Конёнков. Установлено в 1918 году. Демонтировано в 1948 году.</t>
-  </si>
-  <si>
     <t>id_loc</t>
   </si>
   <si>
@@ -795,13 +777,31 @@
   </si>
   <si>
     <t>Кононов_Андрей_Николаевич</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>Обозова_Прасковья_Михайловна ; Кононова_Клавдия_Андреевна</t>
+  </si>
+  <si>
+    <t>Обозова Прасковья Михайловна и др.</t>
+  </si>
+  <si>
+    <t>Обозова Прасковья Михайловна и др. (крупный план)</t>
+  </si>
+  <si>
+    <t>Обозова Прасковья Михайловна (на руках Кононова Клавдия Андреевна), Кононова Мария Петровна с сыновьями (мл. Алексей, Ваисоий, Александр), Леонтьева - мать Марии Петровны, Кононов Николай Спиридонович</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -814,15 +814,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -874,32 +865,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1265,16 +1251,16 @@
         <v>Кононов_Андрей_Николаевич</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="O2"/>
       <c r="P2"/>
@@ -1287,25 +1273,25 @@
         <v>Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="K3"/>
       <c r="O3"/>
@@ -1318,16 +1304,16 @@
         <v>Кононова_Анна_Андреевна</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>253</v>
+      <c r="E4" s="9" t="s">
+        <v>247</v>
       </c>
       <c r="F4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="O4"/>
       <c r="P4"/>
@@ -1339,16 +1325,16 @@
         <v>Кононова_Клавдия_Андреевна</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>253</v>
+      <c r="E5" s="9" t="s">
+        <v>247</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="O5"/>
       <c r="P5"/>
@@ -1360,16 +1346,16 @@
         <v>Кононова_Александра_Андреевна</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -1378,16 +1364,16 @@
         <v>Кононов_Николай_Андреевич</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -1416,19 +1402,19 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1440,611 +1426,611 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
         <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
         <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
         <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
         <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
         <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E30" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
         <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E33" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C34" t="s">
         <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E34" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
         <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E37" t="s">
         <v>36</v>
@@ -2052,16 +2038,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
         <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E38" t="s">
         <v>36</v>
@@ -2069,152 +2055,152 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E39" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E41" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E42" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
         <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E43" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E44" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E45" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
         <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E46" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>23</v>
@@ -2222,16 +2208,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>24</v>
@@ -2254,1156 +2240,1156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>138</v>
+      <c r="A1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>139</v>
+        <v>89</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>140</v>
+      <c r="C3" s="8" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>141</v>
+      <c r="C4" s="8" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>142</v>
+      <c r="C5" s="8" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>143</v>
+      <c r="C6" s="8" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>144</v>
+      <c r="C7" s="8" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>145</v>
+      <c r="C8" s="8" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>146</v>
+      <c r="C9" s="8" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>147</v>
+      <c r="C10" s="8" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>148</v>
+      <c r="C11" s="8" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>149</v>
+      <c r="C12" s="8" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>150</v>
+      <c r="C13" s="8" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>151</v>
+      <c r="C14" s="8" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>152</v>
+      <c r="C15" s="8" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>153</v>
+      <c r="C16" s="8" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>154</v>
+      <c r="C17" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>155</v>
+      <c r="C18" s="8" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>156</v>
+      <c r="C19" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>157</v>
+      <c r="C20" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>132</v>
+      <c r="C21" s="8" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>158</v>
+        <v>100</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>159</v>
+      <c r="C23" s="8" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>160</v>
+      <c r="C24" s="8" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>161</v>
+      <c r="C25" s="8" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>162</v>
+      <c r="C26" s="8" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>163</v>
+      <c r="C27" s="8" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>164</v>
+      <c r="C28" s="8" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>165</v>
+      <c r="C29" s="8" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>166</v>
+      <c r="C30" s="8" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>167</v>
+      <c r="C31" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>150</v>
+      <c r="C32" s="8" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>168</v>
+      <c r="C33" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B34" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>169</v>
+      <c r="C34" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>170</v>
+        <v>70</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>171</v>
+      <c r="C36" s="8" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>172</v>
+      <c r="C37" s="8" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>173</v>
+      <c r="C38" s="8" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>174</v>
+      <c r="C39" s="8" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>175</v>
+      <c r="C40" s="8" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>176</v>
+      <c r="C41" s="8" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>177</v>
+      <c r="C42" s="8" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="9" t="s">
-        <v>178</v>
+      <c r="C43" s="8" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="9" t="s">
-        <v>179</v>
+      <c r="C44" s="8" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>180</v>
+        <v>71</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B46" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>181</v>
+      <c r="C46" s="8" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B47" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>172</v>
+      <c r="C47" s="8" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B48" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>182</v>
+      <c r="C48" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>183</v>
+      <c r="C49" s="8" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>184</v>
+      <c r="C50" s="8" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s">
         <v>47</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>185</v>
+      <c r="C51" s="8" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>186</v>
+      <c r="C52" s="8" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
         <v>49</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>187</v>
+      <c r="C53" s="8" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>176</v>
+      <c r="C54" s="8" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B55" t="s">
         <v>40</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>177</v>
+      <c r="C55" s="8" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B56" t="s">
         <v>50</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>188</v>
+      <c r="C56" s="8" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>178</v>
+      <c r="C57" s="8" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>189</v>
+      <c r="C58" s="8" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
         <v>51</v>
       </c>
-      <c r="C59" s="9" t="s">
-        <v>190</v>
+      <c r="C59" s="8" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>78</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>191</v>
+        <v>72</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B61" t="s">
         <v>35</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>192</v>
+      <c r="C61" s="8" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s">
         <v>46</v>
       </c>
-      <c r="C62" s="9" t="s">
-        <v>193</v>
+      <c r="C62" s="8" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
         <v>37</v>
       </c>
-      <c r="C63" s="9" t="s">
-        <v>182</v>
+      <c r="C63" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B64" t="s">
         <v>0</v>
       </c>
-      <c r="C64" s="9" t="s">
-        <v>183</v>
+      <c r="C64" s="8" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B65" t="s">
         <v>38</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>184</v>
+      <c r="C65" s="8" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
         <v>51</v>
       </c>
-      <c r="C66" s="9" t="s">
-        <v>190</v>
+      <c r="C66" s="8" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s">
         <v>39</v>
       </c>
-      <c r="C67" s="9" t="s">
-        <v>176</v>
+      <c r="C67" s="8" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B68" t="s">
         <v>40</v>
       </c>
-      <c r="C68" s="9" t="s">
-        <v>177</v>
+      <c r="C68" s="8" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B69" t="s">
         <v>50</v>
       </c>
-      <c r="C69" s="9" t="s">
-        <v>188</v>
+      <c r="C69" s="8" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="9" t="s">
-        <v>178</v>
+      <c r="C70" s="8" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
         <v>10</v>
       </c>
-      <c r="C71" s="9" t="s">
-        <v>189</v>
+      <c r="C71" s="8" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>79</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>194</v>
+        <v>73</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>65</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>195</v>
+        <v>59</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B74" t="s">
         <v>36</v>
       </c>
-      <c r="C74" s="9" t="s">
-        <v>193</v>
+      <c r="C74" s="8" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
         <v>37</v>
       </c>
-      <c r="C75" s="9" t="s">
-        <v>182</v>
+      <c r="C75" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B76" t="s">
         <v>0</v>
       </c>
-      <c r="C76" s="9" t="s">
-        <v>183</v>
+      <c r="C76" s="8" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B77" t="s">
         <v>38</v>
       </c>
-      <c r="C77" s="9" t="s">
-        <v>196</v>
+      <c r="C77" s="8" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B78" t="s">
-        <v>66</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>197</v>
+        <v>60</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B79" t="s">
         <v>51</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>198</v>
+      <c r="C79" s="8" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B80" t="s">
-        <v>67</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>199</v>
+        <v>61</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B81" t="s">
         <v>39</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>200</v>
+      <c r="C81" s="8" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B82" t="s">
         <v>40</v>
       </c>
-      <c r="C82" s="9" t="s">
-        <v>177</v>
+      <c r="C82" s="8" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B83" t="s">
         <v>50</v>
       </c>
-      <c r="C83" s="9" t="s">
-        <v>188</v>
+      <c r="C83" s="8" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B84" t="s">
         <v>1</v>
       </c>
-      <c r="C84" s="9" t="s">
-        <v>178</v>
+      <c r="C84" s="8" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
       </c>
-      <c r="C85" s="9" t="s">
-        <v>189</v>
+      <c r="C85" s="8" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B86" t="s">
-        <v>68</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>201</v>
+        <v>62</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>119</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>202</v>
+        <v>113</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B88" t="s">
-        <v>74</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>203</v>
+        <v>68</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B89" t="s">
-        <v>75</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>204</v>
+        <v>69</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B90" t="s">
         <v>51</v>
       </c>
-      <c r="C90" s="9" t="s">
-        <v>205</v>
+      <c r="C90" s="8" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B91" t="s">
-        <v>67</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>199</v>
+        <v>61</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B92" t="s">
         <v>38</v>
       </c>
-      <c r="C92" s="9" t="s">
-        <v>206</v>
+      <c r="C92" s="8" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B93" t="s">
         <v>39</v>
       </c>
-      <c r="C93" s="9" t="s">
-        <v>207</v>
+      <c r="C93" s="8" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B94" t="s">
         <v>40</v>
       </c>
-      <c r="C94" s="9" t="s">
-        <v>208</v>
+      <c r="C94" s="8" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B95" t="s">
         <v>50</v>
       </c>
-      <c r="C95" s="9" t="s">
-        <v>209</v>
+      <c r="C95" s="8" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B96" t="s">
         <v>1</v>
       </c>
-      <c r="C96" s="9" t="s">
-        <v>210</v>
+      <c r="C96" s="8" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="9" t="s">
-        <v>211</v>
+      <c r="C97" s="8" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>76</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>212</v>
+        <v>70</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
-      </c>
-      <c r="C99" s="9" t="s">
-        <v>213</v>
+        <v>71</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B100" t="s">
-        <v>78</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>214</v>
+        <v>72</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>79</v>
-      </c>
-      <c r="C101" s="9" t="s">
-        <v>215</v>
+        <v>73</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>216</v>
-      </c>
-      <c r="C102" s="9" t="s">
-        <v>217</v>
+        <v>210</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B103" t="s">
-        <v>89</v>
-      </c>
-      <c r="C103" s="9" t="s">
-        <v>218</v>
+        <v>83</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B104" t="s">
-        <v>90</v>
-      </c>
-      <c r="C104" s="9" t="s">
-        <v>219</v>
+        <v>84</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B105" t="s">
-        <v>91</v>
-      </c>
-      <c r="C105" s="9" t="s">
-        <v>220</v>
+        <v>85</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
-      </c>
-      <c r="C106" s="9" t="s">
-        <v>221</v>
+        <v>86</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>210</v>
+      </c>
+      <c r="B107" t="s">
+        <v>87</v>
+      </c>
+      <c r="C107" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="B107" t="s">
-        <v>93</v>
-      </c>
-      <c r="C107" s="9" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3422,15 +3408,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3500,10 +3486,10 @@
         <v>Кононов_Андрей_Николаевич__Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
@@ -3563,16 +3549,16 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>38</v>
@@ -3593,53 +3579,53 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>235</v>
+        <v>73</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>56</v>
@@ -3649,10 +3635,10 @@
       </c>
       <c r="G3" s="2"/>
       <c r="M3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="N3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -3936,12 +3922,12 @@
         <v>51</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B2">
         <v>1879</v>
@@ -4051,7 +4037,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -4066,13 +4052,13 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>39</v>
@@ -4090,38 +4076,38 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>календарь-вещи.png</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="7"/>
+      <c r="L2" s="6"/>
       <c r="M2" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -4134,12 +4120,12 @@
   <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="36.42578125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="54" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="43" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="63.85546875" style="5" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" style="5" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="5" customWidth="1"/>
     <col min="10" max="10" width="32.85546875" style="5" customWidth="1"/>
@@ -4180,74 +4166,58 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2">
-        <v>1918</v>
+        <v>245</v>
+      </c>
+      <c r="B2" t="s">
+        <v>248</v>
       </c>
       <c r="C2" t="s">
         <v>41</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
-        <v>Ульянов_Владимир_Ильич-1918.jpg</v>
+        <v>Обозова_Прасковья_Михайловна-max.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>58</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="G2"/>
+      <c r="H2" s="2"/>
       <c r="J2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3">
-        <v>1918</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" t="s">
+        <v>249</v>
       </c>
       <c r="C3" t="s">
         <v>41</v>
       </c>
       <c r="D3" t="str">
         <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
-        <v>Свердлов_Яков_Михайлович-1918.jpg</v>
-      </c>
-      <c r="E3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
+        <v>Обозова_Прасковья_Михайловна-min.jpg</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3" s="2"/>
+      <c r="J3"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H4" s="2"/>
@@ -4333,7 +4303,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -4348,13 +4318,13 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>39</v>
@@ -4372,42 +4342,42 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульяновск_ Ленина_70-2020хх.png</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H2" t="s">
         <v>52</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="7"/>
+        <v>66</v>
+      </c>
+      <c r="L2" s="6"/>
       <c r="N2" t="s">
         <v>20</v>
       </c>
@@ -4439,7 +4409,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -4454,13 +4424,13 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>39</v>
@@ -4478,38 +4448,38 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>календарь-вещи.png</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="7"/>
+      <c r="L2" s="6"/>
       <c r="M2" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="254">
   <si>
     <t>idA</t>
   </si>
@@ -794,7 +794,7 @@
     <t>Обозова Прасковья Михайловна и др. (крупный план)</t>
   </si>
   <si>
-    <t>Обозова Прасковья Михайловна (на руках Кононова Клавдия Андреевна), Кононова Мария Петровна с сыновьями (мл. Алексей, Ваисоий, Александр), Леонтьева - мать Марии Петровны, Кононов Николай Спиридонович</t>
+    <t>Обозова Прасковья Михайловна (на руках Кононова Клавдия Андреевна), Кононова Мария Петровна с сыновьями: Василий, мл. Алексей (на руках), Александр, Леонтьева - мать Марии Петровны, Кононов Николай Спиридонович</t>
   </si>
 </sst>
 </file>
@@ -4217,7 +4217,9 @@
       </c>
       <c r="G3"/>
       <c r="H3" s="2"/>
-      <c r="J3"/>
+      <c r="J3" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H4" s="2"/>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo2\1\family-tree-desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -26,14 +26,14 @@
     <sheet name="version" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$7</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="257">
   <si>
     <t>idA</t>
   </si>
@@ -131,9 +131,6 @@
     <t>marriagePlace_</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>смерть супруга</t>
   </si>
   <si>
@@ -194,15 +191,6 @@
     <t>Ульянов_Илья_Николаевич-Бланк_Мария_Александровна</t>
   </si>
   <si>
-    <t>Семья Ульяновых</t>
-  </si>
-  <si>
-    <t>Слева направо: стоят – Ольга, Александр, Анна; сидят – Мария Александровна с младшей дочерью Марией, Дмитрий, Илья Николаевич, Владимир</t>
-  </si>
-  <si>
-    <t>https://xn--h1aagokeh.xn--p1ai/index.php/journal/post/5232</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Ленин и Свердлов на Красной площади</t>
   </si>
   <si>
@@ -686,9 +674,6 @@
     <t>Перевод на английский</t>
   </si>
   <si>
-    <t>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна</t>
-  </si>
-  <si>
     <t>husband_</t>
   </si>
   <si>
@@ -795,6 +780,30 @@
   </si>
   <si>
     <t>Обозова Прасковья Михайловна (на руках Кононова Клавдия Андреевна), Кононова Мария Петровна с сыновьями: Василий, мл. Алексей (на руках), Александр, Леонтьева - мать Марии Петровны, Кононов Николай Спиридонович</t>
+  </si>
+  <si>
+    <t>Обозова</t>
+  </si>
+  <si>
+    <t>Агафья Ивановна</t>
+  </si>
+  <si>
+    <t>Обозов Михаил Никититич</t>
+  </si>
+  <si>
+    <t>село Луки, Калязинский  район, Тверская область (дорога Москва-Калязин)</t>
+  </si>
+  <si>
+    <t>Обозов_Михаил_Никититич</t>
+  </si>
+  <si>
+    <t>Агафья_Ивановна</t>
+  </si>
+  <si>
+    <t>Обозов_Михаил_Никититич__Агафья_Ивановна</t>
+  </si>
+  <si>
+    <t>Михаил и Агафья Обозовы</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" style="5" customWidth="1"/>
@@ -1245,141 +1254,176 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="str">
-        <f t="shared" ref="A2:A7" si="0">SUBSTITUTE(B2, " ", "_")</f>
-        <v>Кононов_Андрей_Николаевич</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>233</v>
+    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="str">
+        <f t="shared" ref="A2:A9" si="0">SUBSTITUTE(B2, " ", "_")</f>
+        <v>Обозов_Михаил_Никититич</v>
+      </c>
+      <c r="B2" t="s">
+        <v>251</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-    </row>
-    <row r="3" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
+    </row>
+    <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Обозова_Прасковья_Михайловна</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>246</v>
+        <v>Агафья_Ивановна</v>
+      </c>
+      <c r="B3" t="s">
+        <v>250</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="K3"/>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="R3"/>
+      <c r="D3" s="10" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="4" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <f>SUBSTITUTE(B4, " ", "_")</f>
-        <v>Кононова_Анна_Андреевна</v>
+        <f t="shared" si="0"/>
+        <v>Кононов_Андрей_Николаевич</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F4" t="s">
-        <v>245</v>
+        <v>19</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="O4"/>
       <c r="P4"/>
+      <c r="Q4"/>
       <c r="R4"/>
     </row>
     <row r="5" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
-        <v>Кононова_Клавдия_Андреевна</v>
+        <v>Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>247</v>
+      <c r="D5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O5"/>
+        <v>254</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K5"/>
+      <c r="O5" t="s">
+        <v>252</v>
+      </c>
       <c r="P5"/>
       <c r="R5"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="str">
+    <row r="6" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f>SUBSTITUTE(B6, " ", "_")</f>
+        <v>Кононова_Анна_Андреевна</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F6" t="s">
+        <v>240</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="R6"/>
+    </row>
+    <row r="7" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>Кононова_Клавдия_Андреевна</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="R7"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Кононова_Александра_Андреевна</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B8" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="str">
+      <c r="E8" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Кононов_Николай_Андреевич</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B9" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>245</v>
+      <c r="E9" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N7"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:F7">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>
@@ -1402,19 +1446,19 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1426,781 +1470,781 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E35" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E39" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E40" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E41" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E42" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
         <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E44" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E45" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
         <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E46" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>23</v>
@@ -2208,16 +2252,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>24</v>
@@ -2241,1155 +2285,1155 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
         <v>27</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
         <v>28</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
         <v>29</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
         <v>30</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
         <v>0</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B64" t="s">
         <v>0</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B71" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B76" t="s">
         <v>0</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B79" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B83" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B84" t="s">
         <v>1</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B86" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B88" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B89" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B90" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B91" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B92" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B96" t="s">
         <v>1</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B98" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B101" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B103" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B104" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>206</v>
+      </c>
+      <c r="B105" t="s">
+        <v>81</v>
+      </c>
+      <c r="C105" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="B105" t="s">
-        <v>85</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B106" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B107" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3408,15 +3452,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -3486,24 +3530,35 @@
         <v>Кононов_Андрей_Николаевич__Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2" t="s">
         <v>32</v>
       </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3"/>
-      <c r="C3"/>
+      <c r="A3" s="5" t="str">
+        <f>B3&amp;"__"&amp;C3</f>
+        <v>Обозов_Михаил_Никититич__Агафья_Ивановна</v>
+      </c>
+      <c r="B3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4"/>
@@ -3549,28 +3604,28 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -3579,66 +3634,66 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" t="s">
         <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G3" s="2"/>
       <c r="M3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -3725,28 +3780,28 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -3757,29 +3812,29 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>1922</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1922.jpg</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" t="s">
         <v>43</v>
-      </c>
-      <c r="J2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -3880,37 +3935,37 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -3919,44 +3974,32 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B2">
-        <v>1879</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="B2"/>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
-        <v>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна-1879.jpg</v>
+        <v>Обозов_Михаил_Никититич__Агафья_Ивановна-.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1879</v>
-      </c>
-      <c r="L2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2" s="2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J3" s="2"/>
@@ -4037,37 +4080,37 @@
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4076,38 +4119,38 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>календарь-вещи.png</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -4133,31 +4176,31 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>1</v>
@@ -4166,59 +4209,59 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Обозова_Прасковья_Михайловна-max.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G2"/>
       <c r="H2" s="2"/>
       <c r="J2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="str">
         <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
         <v>Обозова_Прасковья_Михайловна-min.jpg</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="2"/>
       <c r="J3" s="5" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -4305,37 +4348,37 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4344,40 +4387,40 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульяновск_ Ленина_70-2020хх.png</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L2" s="6"/>
       <c r="N2" t="s">
@@ -4411,37 +4454,37 @@
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4450,38 +4493,38 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>календарь-вещи.png</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="258">
   <si>
     <t>idA</t>
   </si>
@@ -804,6 +804,9 @@
   </si>
   <si>
     <t>Михаил и Агафья Обозовы</t>
+  </si>
+  <si>
+    <t>Обозов_Михаил_Никититич ; Агафья_Ивановна</t>
   </si>
 </sst>
 </file>
@@ -3999,7 +4002,9 @@
       <c r="J2" s="2"/>
       <c r="L2"/>
       <c r="M2"/>
-      <c r="N2"/>
+      <c r="N2" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J3" s="2"/>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo2\1\family-tree-desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo2\2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="9105"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="277">
   <si>
     <t>idA</t>
   </si>
@@ -807,6 +807,63 @@
   </si>
   <si>
     <t>Обозов_Михаил_Никититич ; Агафья_Ивановна</t>
+  </si>
+  <si>
+    <t>село  Елпатьево, Нагорьевский район, Ярославская область</t>
+  </si>
+  <si>
+    <t>04.11.1916</t>
+  </si>
+  <si>
+    <t>1916</t>
+  </si>
+  <si>
+    <t>23.12.1992</t>
+  </si>
+  <si>
+    <t>1992</t>
+  </si>
+  <si>
+    <t>25.09.1914</t>
+  </si>
+  <si>
+    <t>1914</t>
+  </si>
+  <si>
+    <t>1.12.1998</t>
+  </si>
+  <si>
+    <t>1998</t>
+  </si>
+  <si>
+    <t>24.05.1922</t>
+  </si>
+  <si>
+    <t>1922</t>
+  </si>
+  <si>
+    <t>22.10.2002</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>1927</t>
+  </si>
+  <si>
+    <t>1979</t>
+  </si>
+  <si>
+    <t>Лебедева</t>
+  </si>
+  <si>
+    <t>Новикова</t>
+  </si>
+  <si>
+    <t>Егорушкина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (двое детей мальчик и девочка умерли во младенчестве) </t>
   </si>
 </sst>
 </file>
@@ -1356,13 +1413,30 @@
       <c r="C6" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="D6" s="2" t="s">
+        <v>273</v>
+      </c>
       <c r="E6" s="9" t="s">
         <v>242</v>
       </c>
       <c r="F6" t="s">
         <v>240</v>
       </c>
-      <c r="O6"/>
+      <c r="G6" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="O6" t="s">
+        <v>258</v>
+      </c>
       <c r="P6"/>
       <c r="R6"/>
     </row>
@@ -1377,13 +1451,30 @@
       <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="D7" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="E7" s="9" t="s">
         <v>242</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="O7"/>
+      <c r="G7" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>258</v>
+      </c>
       <c r="P7"/>
       <c r="R7"/>
     </row>
@@ -1398,11 +1489,30 @@
       <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="D8" s="2" t="s">
+        <v>275</v>
+      </c>
       <c r="E8" s="5" t="s">
         <v>242</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>240</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="K8"/>
+      <c r="O8" s="5" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1422,10 +1532,22 @@
       <c r="F9" s="5" t="s">
         <v>240</v>
       </c>
+      <c r="G9" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9"/>
+      <c r="O9" s="5" t="s">
+        <v>258</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N7"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:F7">
       <formula1>$A:$A</formula1>
     </dataValidation>
@@ -3485,6 +3607,7 @@
     <col min="7" max="7" width="13.28515625" style="5" customWidth="1"/>
     <col min="8" max="8" width="11" style="5" customWidth="1"/>
     <col min="9" max="9" width="13.140625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
     <col min="11" max="11" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3541,8 +3664,8 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="J2">
-        <v>4</v>
+      <c r="J2" t="s">
+        <v>276</v>
       </c>
       <c r="K2" t="s">
         <v>32</v>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="9105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="9105" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="288">
   <si>
     <t>idA</t>
   </si>
@@ -864,13 +864,46 @@
   </si>
   <si>
     <t xml:space="preserve">4 (двое детей мальчик и девочка умерли во младенчестве) </t>
+  </si>
+  <si>
+    <t>Лебедев Сергей Михайлович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08.11.1914 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">село Киселево,  Солигалический район,  Вологодская область  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1914 </t>
+  </si>
+  <si>
+    <t>19.05.1999</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>Лебедев_Сергей_Михайлович</t>
+  </si>
+  <si>
+    <t>Кононова_Анна_Андреевна</t>
+  </si>
+  <si>
+    <t>учетно_послужная_карточка</t>
+  </si>
+  <si>
+    <t>учетно послужная карточка</t>
+  </si>
+  <si>
+    <t>https://pamyat-naroda.ru/heroes/person-hero97488769/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D2%26grouppersons%3D1&amp; ; https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -916,6 +949,15 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -934,10 +976,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -953,8 +996,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1233,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" style="5" customWidth="1"/>
@@ -1316,7 +1363,7 @@
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
-        <f t="shared" ref="A2:A9" si="0">SUBSTITUTE(B2, " ", "_")</f>
+        <f t="shared" ref="A2:A10" si="0">SUBSTITUTE(B2, " ", "_")</f>
         <v>Обозов_Михаил_Никититич</v>
       </c>
       <c r="B2" t="s">
@@ -1544,6 +1591,51 @@
       <c r="O9" s="5" t="s">
         <v>258</v>
       </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Лебедев_Сергей_Михайлович</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="O10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N7"/>
@@ -3687,10 +3779,23 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
+      <c r="A4" s="5" t="str">
+        <f>B4&amp;"__"&amp;C4</f>
+        <v>Лебедев_Сергей_Михайлович__Кононова_Анна_Андреевна</v>
+      </c>
+      <c r="B4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
       <c r="E4"/>
+      <c r="J4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5"/>
@@ -4566,14 +4671,14 @@
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" customWidth="1"/>
     <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" customWidth="1"/>
+    <col min="4" max="4" width="56.140625" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+    <col min="8" max="8" width="27.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="11" max="11" width="15.140625" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
@@ -4629,33 +4734,36 @@
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>221</v>
+        <v>283</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
-        <v>календарь-вещи.png</v>
+        <v>Лебедев_Сергей_Михайлович-учетно_послужная_карточка.jpg</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>63</v>
+        <v>283</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>51</v>
+        <v>283</v>
       </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="5" t="s">
-        <v>218</v>
+      <c r="M2" s="11" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" display="https://pamyat-naroda.ru/heroes/person-hero97488769/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D2%26grouppersons%3D1&amp;"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="289">
   <si>
     <t>idA</t>
   </si>
@@ -896,7 +896,10 @@
     <t>учетно послужная карточка</t>
   </si>
   <si>
-    <t>https://pamyat-naroda.ru/heroes/person-hero97488769/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D2%26grouppersons%3D1&amp; ; https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
+    <t xml:space="preserve">https://pamyat-naroda.ru/heroes/person-hero97488769/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D2%26grouppersons%3D1&amp; </t>
+  </si>
+  <si>
+    <t>Есть дубликаты: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
   </si>
 </sst>
 </file>
@@ -4755,7 +4758,9 @@
       <c r="H2" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="L2" s="6"/>
+      <c r="L2" s="6" t="s">
+        <v>288</v>
+      </c>
       <c r="M2" s="11" t="s">
         <v>287</v>
       </c>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo2\2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\tree2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="9105" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="297">
   <si>
     <t>idA</t>
   </si>
@@ -95,9 +95,6 @@
     <t>М</t>
   </si>
   <si>
-    <t>Симбирск</t>
-  </si>
-  <si>
     <t>Ж</t>
   </si>
   <si>
@@ -212,18 +209,9 @@
     <t>synonym_</t>
   </si>
   <si>
-    <t>Ульяновск_ Ленина_70</t>
-  </si>
-  <si>
-    <t>2020хх</t>
-  </si>
-  <si>
     <t>png</t>
   </si>
   <si>
-    <t>Ульяновск, ул. Ленина 70</t>
-  </si>
-  <si>
     <t>Ульянов_Владимир_Ильич; Ульянов_Илья_Николаевич</t>
   </si>
   <si>
@@ -900,6 +888,42 @@
   </si>
   <si>
     <t>Есть дубликаты: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
+  </si>
+  <si>
+    <t>Луки-Елпатьево</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>Села Луки и Елпатьево (5,8 км)</t>
+  </si>
+  <si>
+    <t>Кононов_Андрей_Николаевич__Обозова_Прасковья_Михайловна</t>
+  </si>
+  <si>
+    <t>Тверская \ Ярославская область</t>
+  </si>
+  <si>
+    <t>Кононов_Андрей_Николаевич (Елпатьево) и Обозова_Прасковья_Михайловна (Луки)</t>
+  </si>
+  <si>
+    <t>Обозова Ольга Михайловна</t>
+  </si>
+  <si>
+    <t>Обозова Елизавета Михайловна</t>
+  </si>
+  <si>
+    <t>Обозова Анна Михайловна</t>
+  </si>
+  <si>
+    <t>Дмитриева</t>
+  </si>
+  <si>
+    <t>Ивлева</t>
+  </si>
+  <si>
+    <t>Новопокровская</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" style="5" customWidth="1"/>
@@ -1366,11 +1390,11 @@
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
-        <f t="shared" ref="A2:A10" si="0">SUBSTITUTE(B2, " ", "_")</f>
+        <f t="shared" ref="A2:A13" si="0">SUBSTITUTE(B2, " ", "_")</f>
         <v>Обозов_Михаил_Никититич</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
@@ -1382,13 +1406,13 @@
         <v>Агафья_Ивановна</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1397,16 +1421,16 @@
         <v>Кононов_Андрей_Николаевич</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O4"/>
       <c r="P4"/>
@@ -1419,35 +1443,35 @@
         <v>Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K5"/>
       <c r="O5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="P5"/>
       <c r="R5"/>
@@ -1458,34 +1482,34 @@
         <v>Кононова_Анна_Андреевна</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F6" t="s">
         <v>236</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="F6" t="s">
-        <v>240</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="O6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="P6"/>
       <c r="R6"/>
@@ -1496,34 +1520,34 @@
         <v>Кононова_Клавдия_Андреевна</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="P7"/>
       <c r="R7"/>
@@ -1534,35 +1558,35 @@
         <v>Кононова_Александра_Андреевна</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>242</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="K8"/>
       <c r="O8" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1571,79 +1595,154 @@
         <v>Кононов_Николай_Андреевич</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9"/>
       <c r="O9" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Лебедев_Сергей_Михайлович</v>
+        <v>Обозова_Ольга_Михайловна</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="O10" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Обозова_Елизавета_Михайловна</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Обозова_Анна_Михайловна</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="A13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Лебедев_Сергей_Михайлович</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="O13" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N7"/>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:F7">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:F7 E10:F12">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>
@@ -1666,19 +1765,19 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1690,801 +1789,801 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" t="s">
         <v>96</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E34" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E41" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E42" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E43" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E44" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E45" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D46" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E46" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2505,1155 +2604,1155 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
         <v>0</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
         <v>0</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B71" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B76" t="s">
         <v>0</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B84" t="s">
         <v>1</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B86" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B88" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B89" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B90" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B93" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B96" t="s">
         <v>1</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B99" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B101" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>202</v>
+      </c>
+      <c r="B105" t="s">
+        <v>77</v>
+      </c>
+      <c r="C105" s="8" t="s">
         <v>206</v>
-      </c>
-      <c r="B105" t="s">
-        <v>81</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B107" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3672,15 +3771,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -3711,22 +3810,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -3735,13 +3834,13 @@
         <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="M1" s="1"/>
     </row>
@@ -3751,19 +3850,19 @@
         <v>Кононов_Андрей_Николаевич__Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -3772,13 +3871,13 @@
         <v>Обозов_Михаил_Никититич__Агафья_Ивановна</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -3787,13 +3886,13 @@
         <v>Лебедев_Сергей_Михайлович__Кононова_Анна_Андреевна</v>
       </c>
       <c r="B4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4"/>
       <c r="J4">
@@ -3838,28 +3937,28 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -3868,66 +3967,66 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" t="s">
         <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
         <v>52</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
       </c>
       <c r="G3" s="2"/>
       <c r="M3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -4014,28 +4113,28 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -4046,29 +4145,29 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>1922</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1922.jpg</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" t="s">
         <v>42</v>
-      </c>
-      <c r="J2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -4169,37 +4268,37 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4208,33 +4307,33 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Обозов_Михаил_Никититич__Агафья_Ивановна-.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I2"/>
       <c r="J2" s="2"/>
       <c r="L2"/>
       <c r="M2"/>
       <c r="N2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -4316,37 +4415,37 @@
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4355,38 +4454,38 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>календарь-вещи.png</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4412,31 +4511,31 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>1</v>
@@ -4445,59 +4544,59 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Обозова_Прасковья_Михайловна-max.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G2"/>
       <c r="H2" s="2"/>
       <c r="J2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" t="s">
         <v>240</v>
       </c>
-      <c r="B3" t="s">
-        <v>244</v>
-      </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="str">
         <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
         <v>Обозова_Прасковья_Михайловна-min.jpg</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="2"/>
       <c r="J3" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -4584,37 +4683,37 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4623,45 +4722,41 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>285</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>286</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
-        <v>Ульяновск_ Ленина_70-2020хх.png</v>
+        <v>Луки-Елпатьево-map.png</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>63</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="F2"/>
+      <c r="G2"/>
       <c r="H2" t="s">
-        <v>51</v>
+        <v>288</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L2" s="6"/>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="N2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4690,37 +4785,37 @@
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -4729,40 +4824,40 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Лебедев_Сергей_Михайлович-учетно_послужная_карточка.jpg</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G2" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="M2" s="11" t="s">
         <v>283</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="298">
   <si>
     <t>idA</t>
   </si>
@@ -924,6 +924,9 @@
   </si>
   <si>
     <t>Новопокровская</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ru.wikipedia.org/wiki/%D0%9B%D1%83%D0%BA%D0%B8_(%D0%A2%D0%B2%D0%B5%D1%80%D1%81%D0%BA%D0%B0%D1%8F_%D0%BE%D0%B1%D0%BB%D0%B0%D1%81%D1%82%D1%8C) ; https://ru.wikipedia.org/wiki/%D0%95%D0%BB%D0%BF%D0%B0%D1%82%D1%8C%D0%B5%D0%B2%D0%BE_(%D0%9F%D0%B5%D1%80%D0%B5%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%80%D0%B0%D0%B9%D0%BE%D0%BD) </t>
   </si>
 </sst>
 </file>
@@ -4756,6 +4759,9 @@
       <c r="L2" s="5" t="s">
         <v>290</v>
       </c>
+      <c r="M2" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="N2"/>
     </row>
   </sheetData>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -26,14 +26,14 @@
     <sheet name="version" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="305">
   <si>
     <t>idA</t>
   </si>
@@ -927,6 +927,27 @@
   </si>
   <si>
     <t xml:space="preserve">https://ru.wikipedia.org/wiki/%D0%9B%D1%83%D0%BA%D0%B8_(%D0%A2%D0%B2%D0%B5%D1%80%D1%81%D0%BA%D0%B0%D1%8F_%D0%BE%D0%B1%D0%BB%D0%B0%D1%81%D1%82%D1%8C) ; https://ru.wikipedia.org/wiki/%D0%95%D0%BB%D0%BF%D0%B0%D1%82%D1%8C%D0%B5%D0%B2%D0%BE_(%D0%9F%D0%B5%D1%80%D0%B5%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%80%D0%B0%D0%B9%D0%BE%D0%BD) </t>
+  </si>
+  <si>
+    <t>Кононов Николай Спиридонович</t>
+  </si>
+  <si>
+    <t>Кононов Иван Николаевич</t>
+  </si>
+  <si>
+    <t>Кононов_Николай_Спиридонович</t>
+  </si>
+  <si>
+    <t>Кононов Спиридон</t>
+  </si>
+  <si>
+    <t>Кононов Михаил Спиридонович</t>
+  </si>
+  <si>
+    <t>Кононов_Спиридон</t>
+  </si>
+  <si>
+    <t>кладбище в Елпатьево</t>
   </si>
 </sst>
 </file>
@@ -1310,10 +1331,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" style="5" customWidth="1"/>
     <col min="2" max="2" width="34.42578125" style="5" customWidth="1"/>
     <col min="3" max="3" width="5.42578125" style="5" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" style="5" customWidth="1"/>
@@ -1393,7 +1414,7 @@
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
-        <f t="shared" ref="A2:A13" si="0">SUBSTITUTE(B2, " ", "_")</f>
+        <f t="shared" ref="A2:A17" si="0">SUBSTITUTE(B2, " ", "_")</f>
         <v>Обозов_Михаил_Никититич</v>
       </c>
       <c r="B2" t="s">
@@ -1418,334 +1439,401 @@
         <v>245</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="str">
+    <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Кононов_Спиридон</v>
+      </c>
+      <c r="B4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="Q4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Кононов_Николай_Спиридонович</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Кононов_Михаил_Спиридонович</v>
+      </c>
+      <c r="B6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Кононов_Иван_Николаевич</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>Кононов_Андрей_Николаевич</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
-      <c r="R4"/>
-    </row>
-    <row r="5" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="str">
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+    </row>
+    <row r="9" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>Обозова_Прасковья_Михайловна</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K5"/>
-      <c r="O5" t="s">
+      <c r="K9"/>
+      <c r="O9" t="s">
         <v>248</v>
       </c>
-      <c r="P5"/>
-      <c r="R5"/>
-    </row>
-    <row r="6" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
-        <f>SUBSTITUTE(B6, " ", "_")</f>
+      <c r="P9"/>
+      <c r="R9"/>
+    </row>
+    <row r="10" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f>SUBSTITUTE(B10, " ", "_")</f>
         <v>Кононова_Анна_Андреевна</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F10" t="s">
         <v>236</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O10" t="s">
         <v>254</v>
       </c>
-      <c r="P6"/>
-      <c r="R6"/>
-    </row>
-    <row r="7" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
+      <c r="P10"/>
+      <c r="R10"/>
+    </row>
+    <row r="11" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>Кононова_Клавдия_Андреевна</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O11" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="P7"/>
-      <c r="R7"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="str">
+      <c r="P11"/>
+      <c r="R11"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Кононова_Александра_Андреевна</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="K8"/>
-      <c r="O8" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Кононов_Николай_Андреевич</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9"/>
-      <c r="O9" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Ольга_Михайловна</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Елизавета_Михайловна</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Анна_Михайловна</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K12"/>
+      <c r="O12" s="5" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Лебедев_Сергей_Михайлович</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>273</v>
+        <v>Кононов_Николай_Андреевич</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="E13" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>236</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>274</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="O13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13"/>
+      <c r="O13" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Обозова_Ольга_Михайловна</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Обозова_Елизавета_Михайловна</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Обозова_Анна_Михайловна</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Лебедев_Сергей_Михайлович</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="O17" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N7"/>
+  <autoFilter ref="A1:N11"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:F7 E10:F12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:F11 E14:F16">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -758,9 +758,6 @@
     <t>min</t>
   </si>
   <si>
-    <t>Обозова_Прасковья_Михайловна ; Кононова_Клавдия_Андреевна</t>
-  </si>
-  <si>
     <t>Обозова Прасковья Михайловна и др.</t>
   </si>
   <si>
@@ -948,6 +945,9 @@
   </si>
   <si>
     <t>кладбище в Елпатьево</t>
+  </si>
+  <si>
+    <t>Обозова_Прасковья_Михайловна ; Кононова_Клавдия_Андреевна ; Кононов_Николай_Спиридонович</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1418,7 @@
         <v>Обозов_Михаил_Никититич</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
@@ -1430,13 +1430,13 @@
         <v>Агафья_Ивановна</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1445,14 +1445,14 @@
         <v>Кононов_Спиридон</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="10"/>
       <c r="Q4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1461,14 +1461,14 @@
         <v>Кононов_Николай_Спиридонович</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1477,14 +1477,14 @@
         <v>Кононов_Михаил_Спиридонович</v>
       </c>
       <c r="B6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1493,14 +1493,14 @@
         <v>Кононов_Иван_Николаевич</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1515,7 +1515,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>231</v>
@@ -1543,10 +1543,10 @@
         <v>225</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>227</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K9"/>
       <c r="O9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P9"/>
       <c r="R9"/>
@@ -1579,7 +1579,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>238</v>
@@ -1588,19 +1588,19 @@
         <v>236</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="O10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P10"/>
       <c r="R10"/>
@@ -1617,7 +1617,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>238</v>
@@ -1626,19 +1626,19 @@
         <v>236</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="O11" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P11"/>
       <c r="R11"/>
@@ -1655,7 +1655,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>238</v>
@@ -1664,20 +1664,20 @@
         <v>236</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="K12"/>
       <c r="O12" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -1698,16 +1698,16 @@
         <v>236</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13"/>
       <c r="O13" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1716,19 +1716,19 @@
         <v>Обозова_Ольга_Михайловна</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -1741,19 +1741,19 @@
         <v>Обозова_Елизавета_Михайловна</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1766,19 +1766,19 @@
         <v>Обозова_Анна_Михайловна</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -1791,25 +1791,25 @@
         <v>Лебедев_Сергей_Михайлович</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="O17" t="s">
         <v>274</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="O17" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -3950,7 +3950,7 @@
         <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K2" t="s">
         <v>31</v>
@@ -3962,10 +3962,10 @@
         <v>Обозов_Михаил_Никититич__Агафья_Ивановна</v>
       </c>
       <c r="B3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" t="s">
         <v>249</v>
-      </c>
-      <c r="C3" t="s">
-        <v>250</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>21</v>
@@ -3977,10 +3977,10 @@
         <v>Лебедев_Сергей_Михайлович__Кононова_Анна_Андреевна</v>
       </c>
       <c r="B4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" t="s">
         <v>279</v>
-      </c>
-      <c r="C4" t="s">
-        <v>280</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
@@ -4417,14 +4417,14 @@
         <v>Обозов_Михаил_Никититич__Агафья_Ивановна-.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I2"/>
       <c r="J2" s="2"/>
       <c r="L2"/>
       <c r="M2"/>
       <c r="N2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -4653,15 +4653,15 @@
         <v>Обозова_Прасковья_Михайловна-max.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>241</v>
+        <v>304</v>
       </c>
       <c r="G2"/>
       <c r="H2" s="2"/>
       <c r="J2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4679,15 +4679,15 @@
         <v>Обозова_Прасковья_Михайловна-min.jpg</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>241</v>
+        <v>304</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="2"/>
       <c r="J3" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -4821,10 +4821,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" t="s">
         <v>285</v>
-      </c>
-      <c r="B2" t="s">
-        <v>286</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
@@ -4834,21 +4834,21 @@
         <v>Луки-Елпатьево-map.png</v>
       </c>
       <c r="E2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I2" t="s">
         <v>288</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>290</v>
-      </c>
       <c r="M2" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N2"/>
     </row>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>39</v>
@@ -4939,19 +4939,19 @@
         <v>Лебедев_Сергей_Михайлович-учетно_послужная_карточка.jpg</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="M2" s="11" t="s">
         <v>282</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\tree2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo2\4\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="306">
   <si>
     <t>idA</t>
   </si>
@@ -884,9 +884,6 @@
     <t xml:space="preserve">https://pamyat-naroda.ru/heroes/person-hero97488769/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D2%26grouppersons%3D1&amp; </t>
   </si>
   <si>
-    <t>Есть дубликаты: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
-  </si>
-  <si>
     <t>Луки-Елпатьево</t>
   </si>
   <si>
@@ -948,6 +945,12 @@
   </si>
   <si>
     <t>Обозова_Прасковья_Михайловна ; Кононова_Клавдия_Андреевна ; Кононов_Николай_Спиридонович</t>
+  </si>
+  <si>
+    <t>https://pamyat-naroda.ru/heroes/person-hero97488769/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D2%26grouppersons%3D1&amp; ;  https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
+  </si>
+  <si>
+    <t>На pamyat-naroda.ru много дубликатов: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
   </si>
 </sst>
 </file>
@@ -1445,14 +1448,14 @@
         <v>Кононов_Спиридон</v>
       </c>
       <c r="B4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="10"/>
       <c r="Q4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1461,14 +1464,14 @@
         <v>Кононов_Николай_Спиридонович</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1477,14 +1480,14 @@
         <v>Кононов_Михаил_Спиридонович</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1493,14 +1496,14 @@
         <v>Кононов_Иван_Николаевич</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1515,7 +1518,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>231</v>
@@ -1716,13 +1719,13 @@
         <v>Обозова_Ольга_Михайловна</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>248</v>
@@ -1741,13 +1744,13 @@
         <v>Обозова_Елизавета_Михайловна</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>248</v>
@@ -1766,13 +1769,13 @@
         <v>Обозова_Анна_Михайловна</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>248</v>
@@ -1807,6 +1810,9 @@
       </c>
       <c r="J17" s="2" t="s">
         <v>276</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="O17" t="s">
         <v>274</v>
@@ -1844,7 +1850,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="5" customWidth="1"/>
@@ -2675,6 +2681,210 @@
       </c>
       <c r="E48" s="5" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4496,12 +4706,13 @@
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
     <col min="3" max="3" width="11.140625" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
     <col min="12" max="12" width="18.140625" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4656,7 +4867,7 @@
         <v>242</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G2"/>
       <c r="H2" s="2"/>
@@ -4682,7 +4893,7 @@
         <v>241</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="2"/>
@@ -4821,10 +5032,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B2" t="s">
         <v>284</v>
-      </c>
-      <c r="B2" t="s">
-        <v>285</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
@@ -4834,21 +5045,21 @@
         <v>Луки-Елпатьево-map.png</v>
       </c>
       <c r="E2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
         <v>287</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>289</v>
-      </c>
       <c r="M2" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N2"/>
     </row>
@@ -4948,7 +5159,7 @@
         <v>278</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>282</v>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="307">
   <si>
     <t>idA</t>
   </si>
@@ -951,6 +951,9 @@
   </si>
   <si>
     <t>На pamyat-naroda.ru много дубликатов: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
+  </si>
+  <si>
+    <t>idA_</t>
   </si>
 </sst>
 </file>
@@ -5093,13 +5096,13 @@
         <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>36</v>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="306">
   <si>
     <t>idA</t>
   </si>
@@ -951,9 +951,6 @@
   </si>
   <si>
     <t>На pamyat-naroda.ru много дубликатов: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
-  </si>
-  <si>
-    <t>idA_</t>
   </si>
 </sst>
 </file>
@@ -5096,13 +5093,13 @@
         <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>36</v>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo2\4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo2\5\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="version" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">language!$A$1:$L$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="318">
   <si>
     <t>idA</t>
   </si>
@@ -951,6 +952,42 @@
   </si>
   <si>
     <t>На pamyat-naroda.ru много дубликатов: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
+  </si>
+  <si>
+    <t>id_item_</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>тема</t>
+  </si>
+  <si>
+    <t>extension_</t>
+  </si>
+  <si>
+    <t>тип</t>
+  </si>
+  <si>
+    <t>idA_</t>
+  </si>
+  <si>
+    <t>Отец</t>
+  </si>
+  <si>
+    <t>Мать</t>
+  </si>
+  <si>
+    <t>birth_</t>
+  </si>
+  <si>
+    <t>death_</t>
+  </si>
+  <si>
+    <t>hasFather_</t>
+  </si>
+  <si>
+    <t>hasMother_</t>
   </si>
 </sst>
 </file>
@@ -1339,8 +1376,8 @@
   <cols>
     <col min="1" max="1" width="34.85546875" style="5" customWidth="1"/>
     <col min="2" max="2" width="34.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="31" style="5" customWidth="1"/>
     <col min="6" max="6" width="33.5703125" style="5" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" style="5" customWidth="1"/>
@@ -1850,7 +1887,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="5" customWidth="1"/>
@@ -1969,89 +2006,89 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" t="s">
-        <v>100</v>
+    <row r="7" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -2059,16 +2096,16 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2076,16 +2113,16 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2093,7 +2130,7 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
@@ -2110,7 +2147,7 @@
         <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -2127,7 +2164,7 @@
         <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>36</v>
@@ -2144,7 +2181,7 @@
         <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
         <v>37</v>
@@ -2161,7 +2198,7 @@
         <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
         <v>38</v>
@@ -2178,7 +2215,7 @@
         <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
@@ -2195,7 +2232,7 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -2212,7 +2249,7 @@
         <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>36</v>
@@ -2229,7 +2266,7 @@
         <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
@@ -2246,7 +2283,7 @@
         <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
@@ -2263,7 +2300,7 @@
         <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
@@ -2280,7 +2317,7 @@
         <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
@@ -2297,7 +2334,7 @@
         <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>36</v>
@@ -2314,7 +2351,7 @@
         <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
         <v>37</v>
@@ -2331,7 +2368,7 @@
         <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
         <v>38</v>
@@ -2348,7 +2385,7 @@
         <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
@@ -2365,7 +2402,7 @@
         <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -2384,14 +2421,14 @@
       <c r="B31" t="s">
         <v>65</v>
       </c>
-      <c r="C31" t="s">
-        <v>57</v>
+      <c r="C31" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2399,16 +2436,16 @@
         <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>36</v>
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2416,16 +2453,16 @@
         <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E33" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2433,16 +2470,16 @@
         <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2450,16 +2487,16 @@
         <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2467,16 +2504,16 @@
         <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E36" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2484,16 +2521,16 @@
         <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
+        <v>105</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E37" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2501,16 +2538,16 @@
         <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2518,16 +2555,16 @@
         <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E39" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2535,16 +2572,16 @@
         <v>80</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E40" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2552,16 +2589,16 @@
         <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2569,16 +2606,16 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2586,16 +2623,16 @@
         <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>213</v>
+        <v>106</v>
       </c>
       <c r="E43" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2603,135 +2640,135 @@
         <v>80</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E44" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="A45" t="s">
         <v>80</v>
       </c>
       <c r="B45" t="s">
         <v>81</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E45" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="A46" t="s">
         <v>80</v>
       </c>
       <c r="B46" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" t="s">
+        <v>113</v>
+      </c>
+      <c r="E47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" t="s">
         <v>92</v>
       </c>
-      <c r="C46" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" t="s">
-        <v>120</v>
-      </c>
-      <c r="E46" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B47" s="5" t="s">
+      <c r="C48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" t="s">
+        <v>213</v>
+      </c>
+      <c r="E48" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>100</v>
+      <c r="C49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>96</v>
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>102</v>
+      <c r="B51" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" t="s">
+        <v>120</v>
+      </c>
+      <c r="E51" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2739,16 +2776,16 @@
         <v>80</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>220</v>
+        <v>92</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2756,16 +2793,16 @@
         <v>80</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>220</v>
+        <v>92</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>90</v>
+        <v>212</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2775,14 +2812,14 @@
       <c r="B54" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>57</v>
+      <c r="C54" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2790,16 +2827,16 @@
         <v>80</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>36</v>
+        <v>220</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2807,16 +2844,16 @@
         <v>80</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2824,16 +2861,16 @@
         <v>80</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2841,16 +2878,16 @@
         <v>80</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2858,16 +2895,16 @@
         <v>80</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2877,17 +2914,171 @@
       <c r="B60" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>104</v>
       </c>
     </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:L69"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
@@ -5076,7 +5267,7 @@
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
     <col min="2" max="2" width="32.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
     <col min="4" max="4" width="56.140625" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -948,9 +948,6 @@
     <t>Обозова_Прасковья_Михайловна ; Кононова_Клавдия_Андреевна ; Кононов_Николай_Спиридонович</t>
   </si>
   <si>
-    <t>https://pamyat-naroda.ru/heroes/person-hero97488769/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D2%26grouppersons%3D1&amp; ;  https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
-  </si>
-  <si>
     <t>На pamyat-naroda.ru много дубликатов: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
   </si>
   <si>
@@ -988,6 +985,9 @@
   </si>
   <si>
     <t>hasMother_</t>
+  </si>
+  <si>
+    <t>./md_person/Лебедев_Сергей_Михайлович.md ; https://pamyat-naroda.ru/heroes/person-hero97488769/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D2%26grouppersons%3D1&amp; ;  https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1849,7 @@
         <v>276</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="O17" t="s">
         <v>274</v>
@@ -2014,13 +2014,13 @@
         <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2031,10 +2031,10 @@
         <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>4</v>
@@ -2048,10 +2048,10 @@
         <v>81</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>5</v>
@@ -2065,7 +2065,7 @@
         <v>81</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>86</v>
@@ -2082,7 +2082,7 @@
         <v>81</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>88</v>
@@ -3017,13 +3017,13 @@
         <v>219</v>
       </c>
       <c r="C66" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>307</v>
-      </c>
       <c r="E66" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3037,7 +3037,7 @@
         <v>44</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>34</v>
@@ -3051,10 +3051,10 @@
         <v>219</v>
       </c>
       <c r="C68" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>309</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>310</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>35</v>
@@ -3068,13 +3068,13 @@
         <v>219</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -5350,7 +5350,7 @@
         <v>278</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>282</v>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -27,14 +27,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">language!$A$1:$L$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$13</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="322">
   <si>
     <t>idA</t>
   </si>
@@ -988,6 +988,18 @@
   </si>
   <si>
     <t>./md_person/Лебедев_Сергей_Михайлович.md ; https://pamyat-naroda.ru/heroes/person-hero97488769/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D2%26grouppersons%3D1&amp; ;  https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
+  </si>
+  <si>
+    <t>Леонтьева Мария Петровна</t>
+  </si>
+  <si>
+    <t>Леонтьева</t>
+  </si>
+  <si>
+    <t>Леонтьева_Мария_Петровна</t>
+  </si>
+  <si>
+    <t>Кононов_Иван_Николаевич</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" style="5" customWidth="1"/>
@@ -1454,7 +1466,7 @@
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
-        <f t="shared" ref="A2:A17" si="0">SUBSTITUTE(B2, " ", "_")</f>
+        <f t="shared" ref="A2:A19" si="0">SUBSTITUTE(B2, " ", "_")</f>
         <v>Обозов_Михаил_Никититич</v>
       </c>
       <c r="B2" t="s">
@@ -1543,276 +1555,259 @@
         <v>298</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
+    <row r="8" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Леонтьева_Мария_Петровна</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Леонтьева</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>Кононов_Андрей_Николаевич</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="O8"/>
-      <c r="P8"/>
-      <c r="Q8"/>
-      <c r="R8"/>
-    </row>
-    <row r="9" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Прасковья_Михайловна</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K9"/>
-      <c r="O9" t="s">
-        <v>247</v>
-      </c>
-      <c r="P9"/>
-      <c r="R9"/>
-    </row>
-    <row r="10" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f>SUBSTITUTE(B10, " ", "_")</f>
-        <v>Кононова_Анна_Андреевна</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="F10" t="s">
-        <v>236</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O10" t="s">
-        <v>253</v>
-      </c>
+      <c r="O10"/>
       <c r="P10"/>
+      <c r="Q10"/>
       <c r="R10"/>
     </row>
     <row r="11" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
-        <v>Кононова_Клавдия_Андреевна</v>
+        <v>Обозова_Прасковья_Михайловна</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>238</v>
+        <v>225</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>253</v>
+        <v>228</v>
+      </c>
+      <c r="K11"/>
+      <c r="O11" t="s">
+        <v>247</v>
       </c>
       <c r="P11"/>
       <c r="R11"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="str">
+    <row r="12" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f>SUBSTITUTE(B12, " ", "_")</f>
+        <v>Кононова_Анна_Андреевна</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F12" t="s">
+        <v>236</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="O12" t="s">
+        <v>253</v>
+      </c>
+      <c r="P12"/>
+      <c r="R12"/>
+    </row>
+    <row r="13" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f t="shared" si="0"/>
+        <v>Кононова_Клавдия_Андреевна</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="P13"/>
+      <c r="R13"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Кононова_Александра_Андреевна</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="K12"/>
-      <c r="O12" s="5" t="s">
+      <c r="K14"/>
+      <c r="O14" s="5" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="str">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Кононов_Николай_Андреевич</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2" t="s">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13"/>
-      <c r="O13" s="5" t="s">
+      <c r="J15" s="2"/>
+      <c r="K15"/>
+      <c r="O15" s="5" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Ольга_Михайловна</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Елизавета_Михайловна</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Обозова_Анна_Михайловна</v>
+        <v>Обозова_Ольга_Михайловна</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>292</v>
+      <c r="D16" s="2" t="s">
+        <v>294</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>248</v>
@@ -1825,47 +1820,85 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Лебедев_Сергей_Михайлович</v>
+        <v>Обозова_Елизавета_Михайловна</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="O17" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Обозова_Анна_Михайловна</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="A19" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Лебедев_Сергей_Михайлович</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="O19" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G20" s="2"/>
@@ -1873,10 +1906,22 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N11"/>
+  <autoFilter ref="A1:N13"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:F11 E14:F16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:F13 E16:F18">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>
@@ -4392,9 +4437,19 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
+      <c r="A5" s="5" t="str">
+        <f>B5&amp;"__"&amp;C5</f>
+        <v>Кононов_Иван_Николаевич__Леонтьева_Мария_Петровна</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="E5"/>
     </row>
   </sheetData>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -945,9 +945,6 @@
     <t>кладбище в Елпатьево</t>
   </si>
   <si>
-    <t>Обозова_Прасковья_Михайловна ; Кононова_Клавдия_Андреевна ; Кононов_Николай_Спиридонович</t>
-  </si>
-  <si>
     <t>На pamyat-naroda.ru много дубликатов: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
   </si>
   <si>
@@ -1000,6 +997,9 @@
   </si>
   <si>
     <t>Кононов_Иван_Николаевич</t>
+  </si>
+  <si>
+    <t>Обозова_Прасковья_Михайловна ; Кононова_Клавдия_Андреевна ; Кононов_Николай_Спиридонович ; Леонтьева_Мария_Петровна ; Леонтьева</t>
   </si>
 </sst>
 </file>
@@ -1561,7 +1561,7 @@
         <v>Леонтьева_Мария_Петровна</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1580,7 +1580,7 @@
         <v>Леонтьева</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
@@ -1894,7 +1894,7 @@
         <v>276</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O19" t="s">
         <v>274</v>
@@ -2059,13 +2059,13 @@
         <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2076,10 +2076,10 @@
         <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>4</v>
@@ -2093,10 +2093,10 @@
         <v>81</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>5</v>
@@ -2110,7 +2110,7 @@
         <v>81</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>86</v>
@@ -2127,7 +2127,7 @@
         <v>81</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>88</v>
@@ -3062,13 +3062,13 @@
         <v>219</v>
       </c>
       <c r="C66" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>306</v>
-      </c>
       <c r="E66" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3082,7 +3082,7 @@
         <v>44</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>34</v>
@@ -3096,10 +3096,10 @@
         <v>219</v>
       </c>
       <c r="C68" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>308</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>309</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>35</v>
@@ -3113,13 +3113,13 @@
         <v>219</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -4442,10 +4442,10 @@
         <v>Кононов_Иван_Николаевич__Леонтьева_Мария_Петровна</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>21</v>
@@ -5113,7 +5113,7 @@
         <v>242</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="G2"/>
       <c r="H2" s="2"/>
@@ -5139,7 +5139,7 @@
         <v>241</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="2"/>
@@ -5405,7 +5405,7 @@
         <v>278</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>282</v>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -27,14 +27,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">language!$A$1:$L$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$16</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="327">
   <si>
     <t>idA</t>
   </si>
@@ -1000,6 +1000,21 @@
   </si>
   <si>
     <t>Обозова_Прасковья_Михайловна ; Кононова_Клавдия_Андреевна ; Кононов_Николай_Спиридонович ; Леонтьева_Мария_Петровна ; Леонтьева</t>
+  </si>
+  <si>
+    <t>из- Лихарева</t>
+  </si>
+  <si>
+    <t>Сухарникова Акулина</t>
+  </si>
+  <si>
+    <t>Кононов Василий Николаевич</t>
+  </si>
+  <si>
+    <t>Кононова Устинья Николаевна</t>
+  </si>
+  <si>
+    <t>Сухарникова_Акулина</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" style="5" customWidth="1"/>
@@ -1403,6 +1418,7 @@
     <col min="16" max="16" width="13.7109375" customWidth="1"/>
     <col min="17" max="17" width="14.28515625" customWidth="1"/>
     <col min="18" max="18" width="13.7109375" customWidth="1"/>
+    <col min="19" max="19" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1466,7 +1482,7 @@
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
-        <f t="shared" ref="A2:A19" si="0">SUBSTITUTE(B2, " ", "_")</f>
+        <f t="shared" ref="A2:A22" si="0">SUBSTITUTE(B2, " ", "_")</f>
         <v>Обозов_Михаил_Никититич</v>
       </c>
       <c r="B2" t="s">
@@ -1588,340 +1604,389 @@
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
+    <row r="10" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Кононов_Андрей_Николаевич</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>224</v>
+        <v>Сухарникова_Акулина</v>
+      </c>
+      <c r="B10" t="s">
+        <v>323</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="2"/>
+      <c r="O10" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Кононов_Василий_Николаевич</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
-      <c r="R10"/>
-    </row>
-    <row r="11" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
+    </row>
+    <row r="12" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Обозова_Прасковья_Михайловна</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K11"/>
-      <c r="O11" t="s">
-        <v>247</v>
-      </c>
-      <c r="P11"/>
-      <c r="R11"/>
-    </row>
-    <row r="12" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="str">
-        <f>SUBSTITUTE(B12, " ", "_")</f>
-        <v>Кононова_Анна_Андреевна</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>232</v>
+        <v>Кононова_Устинья_Николаевна</v>
+      </c>
+      <c r="B12" t="s">
+        <v>325</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="F12" t="s">
-        <v>236</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O12" t="s">
-        <v>253</v>
-      </c>
-      <c r="P12"/>
-      <c r="R12"/>
+        <v>19</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="2" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="13" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
+        <v>Кононов_Андрей_Николаевич</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+    </row>
+    <row r="14" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f t="shared" si="0"/>
+        <v>Обозова_Прасковья_Михайловна</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K14"/>
+      <c r="O14" t="s">
+        <v>247</v>
+      </c>
+      <c r="P14"/>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f>SUBSTITUTE(B15, " ", "_")</f>
+        <v>Кононова_Анна_Андреевна</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F15" t="s">
+        <v>236</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="O15" t="s">
+        <v>253</v>
+      </c>
+      <c r="P15"/>
+      <c r="R15"/>
+    </row>
+    <row r="16" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f t="shared" si="0"/>
         <v>Кононова_Клавдия_Андреевна</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="O13" s="5" t="s">
+      <c r="O16" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="P13"/>
-      <c r="R13"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="str">
+      <c r="P16"/>
+      <c r="R16"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Кононова_Александра_Андреевна</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="K14"/>
-      <c r="O14" s="5" t="s">
+      <c r="K17"/>
+      <c r="O17" s="5" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="str">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Кононов_Николай_Андреевич</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2" t="s">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15"/>
-      <c r="O15" s="5" t="s">
+      <c r="J18" s="2"/>
+      <c r="K18"/>
+      <c r="O18" s="5" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="str">
+    <row r="19" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Обозова_Ольга_Михайловна</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="str">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Обозова_Елизавета_Михайловна</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Анна_Михайловна</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Лебедев_Сергей_Михайлович</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="O19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Обозова_Анна_Михайловна</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="A22" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Лебедев_Сергей_Михайлович</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="O22" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N13"/>
+  <autoFilter ref="A1:N16"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:F13 E16:F18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:F16 E19:F21 E10:E12">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>
@@ -4327,7 +4392,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.42578125" style="5" customWidth="1"/>
@@ -4452,9 +4517,24 @@
       </c>
       <c r="E5"/>
     </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="str">
+        <f>B6&amp;"__"&amp;C6</f>
+        <v>Кононов_Николай_Спиридонович__Сухарникова_Акулина</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B6">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -900,9 +900,6 @@
     <t>Тверская \ Ярославская область</t>
   </si>
   <si>
-    <t>Кононов_Андрей_Николаевич (Елпатьево) и Обозова_Прасковья_Михайловна (Луки)</t>
-  </si>
-  <si>
     <t>Обозова Ольга Михайловна</t>
   </si>
   <si>
@@ -921,9 +918,6 @@
     <t>Новопокровская</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ru.wikipedia.org/wiki/%D0%9B%D1%83%D0%BA%D0%B8_(%D0%A2%D0%B2%D0%B5%D1%80%D1%81%D0%BA%D0%B0%D1%8F_%D0%BE%D0%B1%D0%BB%D0%B0%D1%81%D1%82%D1%8C) ; https://ru.wikipedia.org/wiki/%D0%95%D0%BB%D0%BF%D0%B0%D1%82%D1%8C%D0%B5%D0%B2%D0%BE_(%D0%9F%D0%B5%D1%80%D0%B5%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%80%D0%B0%D0%B9%D0%BE%D0%BD) </t>
-  </si>
-  <si>
     <t>Кононов Николай Спиридонович</t>
   </si>
   <si>
@@ -1015,6 +1009,12 @@
   </si>
   <si>
     <t>Сухарникова_Акулина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кононовы (Елпатьево) - Обозовы (Луки), а также Сухарниковы (Лихарево)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../md_location/Луки-Елпатьево.md ; https://ru.wikipedia.org/wiki/%D0%9B%D1%83%D0%BA%D0%B8_(%D0%A2%D0%B2%D0%B5%D1%80%D1%81%D0%BA%D0%B0%D1%8F_%D0%BE%D0%B1%D0%BB%D0%B0%D1%81%D1%82%D1%8C) ; https://ru.wikipedia.org/wiki/%D0%95%D0%BB%D0%BF%D0%B0%D1%82%D1%8C%D0%B5%D0%B2%D0%BE_(%D0%9F%D0%B5%D1%80%D0%B5%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%80%D0%B0%D0%B9%D0%BE%D0%BD) </t>
   </si>
 </sst>
 </file>
@@ -1513,14 +1513,14 @@
         <v>Кононов_Спиридон</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="10"/>
       <c r="Q4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1529,14 +1529,14 @@
         <v>Кононов_Николай_Спиридонович</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1545,14 +1545,14 @@
         <v>Кононов_Михаил_Спиридонович</v>
       </c>
       <c r="B6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1561,14 +1561,14 @@
         <v>Кононов_Иван_Николаевич</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1577,7 +1577,7 @@
         <v>Леонтьева_Мария_Петровна</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1596,7 +1596,7 @@
         <v>Леонтьева</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
@@ -1610,7 +1610,7 @@
         <v>Сухарникова_Акулина</v>
       </c>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>20</v>
@@ -1618,7 +1618,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="2"/>
       <c r="O10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1627,14 +1627,14 @@
         <v>Кононов_Василий_Николаевич</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1643,14 +1643,14 @@
         <v>Кононова_Устинья_Николаевна</v>
       </c>
       <c r="B12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1665,7 +1665,7 @@
         <v>19</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>231</v>
@@ -1866,13 +1866,13 @@
         <v>Обозова_Ольга_Михайловна</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>248</v>
@@ -1891,13 +1891,13 @@
         <v>Обозова_Елизавета_Михайловна</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>248</v>
@@ -1916,13 +1916,13 @@
         <v>Обозова_Анна_Михайловна</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>248</v>
@@ -1959,7 +1959,7 @@
         <v>276</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="O22" t="s">
         <v>274</v>
@@ -2124,13 +2124,13 @@
         <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2141,10 +2141,10 @@
         <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>4</v>
@@ -2158,10 +2158,10 @@
         <v>81</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>5</v>
@@ -2175,7 +2175,7 @@
         <v>81</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>86</v>
@@ -2192,7 +2192,7 @@
         <v>81</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>88</v>
@@ -3127,13 +3127,13 @@
         <v>219</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3147,7 +3147,7 @@
         <v>44</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>34</v>
@@ -3161,10 +3161,10 @@
         <v>219</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>35</v>
@@ -3178,13 +3178,13 @@
         <v>219</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4507,10 +4507,10 @@
         <v>Кононов_Иван_Николаевич__Леонтьева_Мария_Петровна</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>21</v>
@@ -4523,10 +4523,10 @@
         <v>Кононов_Николай_Спиридонович__Сухарникова_Акулина</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>21</v>
@@ -5193,7 +5193,7 @@
         <v>242</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G2"/>
       <c r="H2" s="2"/>
@@ -5219,7 +5219,7 @@
         <v>241</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="2"/>
@@ -5382,10 +5382,10 @@
         <v>287</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>288</v>
+        <v>325</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="N2"/>
     </row>
@@ -5485,7 +5485,7 @@
         <v>278</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>282</v>

--- a/ver6/tree.xlsx
+++ b/ver6/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo2\5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\tree2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="8580" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="8610"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -27,14 +27,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">language!$A$1:$L$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$19</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="331">
   <si>
     <t>idA</t>
   </si>
@@ -777,9 +777,6 @@
     <t>Обозов Михаил Никититич</t>
   </si>
   <si>
-    <t>село Луки, Калязинский  район, Тверская область (дорога Москва-Калязин)</t>
-  </si>
-  <si>
     <t>Обозов_Михаил_Никититич</t>
   </si>
   <si>
@@ -795,9 +792,6 @@
     <t>Обозов_Михаил_Никититич ; Агафья_Ивановна</t>
   </si>
   <si>
-    <t>село  Елпатьево, Нагорьевский район, Ярославская область</t>
-  </si>
-  <si>
     <t>04.11.1916</t>
   </si>
   <si>
@@ -936,9 +930,6 @@
     <t>Кононов_Спиридон</t>
   </si>
   <si>
-    <t>кладбище в Елпатьево</t>
-  </si>
-  <si>
     <t>На pamyat-naroda.ru много дубликатов: https://pamyat-naroda.ru/heroes/isp-chelovek_spisok11516542/?backurl=%2Fheroes%2F%3Fadv_search%3Dy%26last_name%3D%D0%9B%D0%B5%D0%B1%D0%B5%D0%B4%D0%B5%D0%B2%26first_name%3D%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9%20%26middle_name%3D%D0%9C%D0%B8%D1%85%D0%B0%D0%B9%D0%BB%D0%BE%D0%B2%D0%B8%D1%87%26date_birth_from%3D1914%26static_hash%3Dc1f55066a911bfb276a602504c5715e8b3573f3600cdbc1aa8742bd494516397v7%26place_birth_ids%3D%26division_ids%3D%26group%3Dall%26types%3Dpamyat_commander%3Anagrady_nagrad_doc%3Anagrady_uchet_kartoteka%3Anagrady_ubilein_kartoteka%3Apdv_kart_in%3Apdv_kart_in_inostranec%3Apamyat_voenkomat%3Apotery_vpp%3Apamyat_zsp_parts%3Akld_ran%3Akld_bolezn%3Akld_card%3Akld_upk%3Akld_vmf%3Akld_partizan%3Apotery_doneseniya_o_poteryah%3Apotery_gospitali%3Apotery_utochenie_poter%3Apotery_spiski_zahoroneniy%3Apotery_voennoplen%3Apotery_iskluchenie_iz_spiskov%3Apotery_kartoteki%3Apotery_rvk_extra%3Apotery_isp_extra%3Asame_doroga%3Asame_rvk%3Asame_guk%3Apotery_knigi_pamyati%26page%3D1%26grouppersons%3D1&amp;</t>
   </si>
   <si>
@@ -996,9 +987,6 @@
     <t>Обозова_Прасковья_Михайловна ; Кононова_Клавдия_Андреевна ; Кононов_Николай_Спиридонович ; Леонтьева_Мария_Петровна ; Леонтьева</t>
   </si>
   <si>
-    <t>из- Лихарева</t>
-  </si>
-  <si>
     <t>Сухарникова Акулина</t>
   </si>
   <si>
@@ -1015,13 +1003,37 @@
   </si>
   <si>
     <t xml:space="preserve">../md_location/Луки-Елпатьево.md ; https://ru.wikipedia.org/wiki/%D0%9B%D1%83%D0%BA%D0%B8_(%D0%A2%D0%B2%D0%B5%D1%80%D1%81%D0%BA%D0%B0%D1%8F_%D0%BE%D0%B1%D0%BB%D0%B0%D1%81%D1%82%D1%8C) ; https://ru.wikipedia.org/wiki/%D0%95%D0%BB%D0%BF%D0%B0%D1%82%D1%8C%D0%B5%D0%B2%D0%BE_(%D0%9F%D0%B5%D1%80%D0%B5%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%80%D0%B0%D0%B9%D0%BE%D0%BD) </t>
+  </si>
+  <si>
+    <t>Лихарево</t>
+  </si>
+  <si>
+    <t>Луки</t>
+  </si>
+  <si>
+    <t>Елпатьево</t>
+  </si>
+  <si>
+    <t>Обозов Никита</t>
+  </si>
+  <si>
+    <t>Обозова Ульяна</t>
+  </si>
+  <si>
+    <t>Обозова Татьяна</t>
+  </si>
+  <si>
+    <t>Обозов_Никита</t>
+  </si>
+  <si>
+    <t>Обозова_Ульяна</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1076,6 +1088,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1098,7 +1118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1117,6 +1137,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1398,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" style="5" customWidth="1"/>
@@ -1482,11 +1503,11 @@
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
-        <f t="shared" ref="A2:A22" si="0">SUBSTITUTE(B2, " ", "_")</f>
-        <v>Обозов_Михаил_Никититич</v>
-      </c>
-      <c r="B2" t="s">
-        <v>246</v>
+        <f t="shared" ref="A2:A4" si="0">SUBSTITUTE(B2, " ", "_")</f>
+        <v>Обозов_Никита</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>326</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
@@ -1495,498 +1516,552 @@
     <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Агафья_Ивановна</v>
-      </c>
-      <c r="B3" t="s">
-        <v>245</v>
+        <v>Обозова_Ульяна</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>327</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Кононов_Спиридон</v>
-      </c>
-      <c r="B4" t="s">
-        <v>297</v>
+        <v>Обозова_Татьяна</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>328</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="Q4" t="s">
-        <v>300</v>
+        <v>20</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Кононов_Николай_Спиридонович</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>294</v>
+        <f t="shared" ref="A5:A25" si="1">SUBSTITUTE(B5, " ", "_")</f>
+        <v>Обозов_Михаил_Никититич</v>
+      </c>
+      <c r="B5" t="s">
+        <v>246</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>299</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="P5" s="10"/>
     </row>
     <row r="6" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Кононов_Михаил_Спиридонович</v>
+        <f t="shared" si="1"/>
+        <v>Агафья_Ивановна</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10" t="s">
-        <v>299</v>
+        <v>20</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Кононов_Иван_Николаевич</v>
-      </c>
-      <c r="B7" s="2" t="s">
+        <f t="shared" si="1"/>
+        <v>Кононов_Спиридон</v>
+      </c>
+      <c r="B7" t="s">
         <v>295</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="10"/>
-      <c r="E7" s="10" t="s">
-        <v>296</v>
+      <c r="Q7" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Леонтьева_Мария_Петровна</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>315</v>
+        <f t="shared" si="1"/>
+        <v>Кононов_Николай_Спиридонович</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>292</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10" t="s">
-        <v>316</v>
+        <v>19</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Леонтьева</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>316</v>
+        <f t="shared" si="1"/>
+        <v>Кононов_Михаил_Спиридонович</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
+      <c r="E9" s="10" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="10" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Сухарникова_Акулина</v>
-      </c>
-      <c r="B10" t="s">
-        <v>321</v>
+        <f t="shared" si="1"/>
+        <v>Кононов_Иван_Николаевич</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="10"/>
-      <c r="E10" s="2"/>
-      <c r="O10" t="s">
-        <v>320</v>
+      <c r="E10" s="10" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Кононов_Василий_Николаевич</v>
+        <f t="shared" si="1"/>
+        <v>Леонтьева_Мария_Петровна</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="2" t="s">
-        <v>296</v>
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>Леонтьева</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Сухарникова_Акулина</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="O13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Кононов_Василий_Николаевич</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="str">
+        <f t="shared" si="1"/>
         <v>Кононова_Устинья_Николаевна</v>
       </c>
-      <c r="B12" t="s">
-        <v>323</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B15" t="s">
+        <v>319</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="str">
-        <f t="shared" si="0"/>
-        <v>Кононов_Андрей_Николаевич</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="O13"/>
-      <c r="P13"/>
-      <c r="Q13"/>
-      <c r="R13"/>
-    </row>
-    <row r="14" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Прасковья_Михайловна</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K14"/>
-      <c r="O14" t="s">
-        <v>247</v>
-      </c>
-      <c r="P14"/>
-      <c r="R14"/>
-    </row>
-    <row r="15" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="str">
-        <f>SUBSTITUTE(B15, " ", "_")</f>
-        <v>Кононова_Анна_Андреевна</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="F15" t="s">
-        <v>236</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O15" t="s">
-        <v>253</v>
-      </c>
-      <c r="P15"/>
-      <c r="R15"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="2" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="16" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
-        <f t="shared" si="0"/>
-        <v>Кононова_Клавдия_Андреевна</v>
+        <f t="shared" si="1"/>
+        <v>Кононов_Андрей_Николаевич</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>236</v>
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>294</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>253</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="O16"/>
       <c r="P16"/>
+      <c r="Q16"/>
       <c r="R16"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Кононова_Александра_Андреевна</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>234</v>
+    <row r="17" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f t="shared" si="1"/>
+        <v>Обозова_Прасковья_Михайловна</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>237</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E17" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K17"/>
+      <c r="O17" t="s">
+        <v>324</v>
+      </c>
+      <c r="P17"/>
+      <c r="R17"/>
+    </row>
+    <row r="18" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <f>SUBSTITUTE(B18, " ", "_")</f>
+        <v>Кононова_Анна_Андреевна</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F18" t="s">
         <v>236</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K17"/>
-      <c r="O17" s="5" t="s">
+      <c r="G18" s="2" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Кононов_Николай_Андреевич</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="I18" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="J18" s="2"/>
-      <c r="K18"/>
-      <c r="O18" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Ольга_Михайловна</v>
+        <v>255</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="O18" t="s">
+        <v>325</v>
+      </c>
+      <c r="P18"/>
+      <c r="R18"/>
+    </row>
+    <row r="19" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <f t="shared" si="1"/>
+        <v>Кононова_Клавдия_Андреевна</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>248</v>
+        <v>267</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>238</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="P19"/>
+      <c r="R19"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Елизавета_Михайловна</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>289</v>
+        <f t="shared" si="1"/>
+        <v>Кононова_Александра_Андреевна</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E20" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K20"/>
+      <c r="O20" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Кононов_Николай_Андреевич</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21"/>
+      <c r="O21" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Обозова_Ольга_Михайловна</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Обозова_Анна_Михайловна</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Обозова_Елизавета_Михайловна</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="E23" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Лебедев_Сергей_Михайлович</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="O22" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Обозова_Анна_Михайловна</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Лебедев_Сергей_Михайлович</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="O25" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N16"/>
+  <autoFilter ref="A1:N19"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:F16 E19:F21 E10:E12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16:F19 E22:F24 E13:E15">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>
@@ -2124,13 +2199,13 @@
         <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2141,10 +2216,10 @@
         <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>4</v>
@@ -2158,10 +2233,10 @@
         <v>81</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>5</v>
@@ -2175,7 +2250,7 @@
         <v>81</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>86</v>
@@ -2192,7 +2267,7 @@
         <v>81</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>88</v>
@@ -3127,13 +3202,13 @@
         <v>219</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3147,7 +3222,7 @@
         <v>44</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>34</v>
@@ -3161,10 +3236,10 @@
         <v>219</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>35</v>
@@ -3178,13 +3253,13 @@
         <v>219</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -4392,7 +4467,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.42578125" style="5" customWidth="1"/>
@@ -4446,95 +4521,119 @@
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="str">
+    <row r="2" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="str">
         <f>B2&amp;"__"&amp;C2</f>
+        <v>Обозов_Никита__Обозова_Ульяна</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <f>B3&amp;"__"&amp;C3</f>
         <v>Кононов_Андрей_Николаевич__Обозова_Прасковья_Михайловна</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>236</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="J2" t="s">
-        <v>271</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J3" t="s">
+        <v>269</v>
+      </c>
+      <c r="K3" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="str">
-        <f>B3&amp;"__"&amp;C3</f>
-        <v>Обозов_Михаил_Никититич__Агафья_Ивановна</v>
-      </c>
-      <c r="B3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>B4&amp;"__"&amp;C4</f>
-        <v>Лебедев_Сергей_Михайлович__Кононова_Анна_Андреевна</v>
+        <v>Обозов_Михаил_Никититич__Агафья_Ивановна</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>247</v>
       </c>
       <c r="C4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="E4"/>
-      <c r="J4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="str">
         <f>B5&amp;"__"&amp;C5</f>
-        <v>Кононов_Иван_Николаевич__Леонтьева_Мария_Петровна</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>318</v>
+        <v>Лебедев_Сергей_Михайлович__Кононова_Анна_Андреевна</v>
+      </c>
+      <c r="B5" t="s">
+        <v>276</v>
       </c>
       <c r="C5" t="s">
-        <v>317</v>
-      </c>
-      <c r="D5" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
       <c r="E5"/>
+      <c r="J5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="str">
         <f>B6&amp;"__"&amp;C6</f>
-        <v>Кононов_Николай_Спиридонович__Сухарникова_Акулина</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>324</v>
+        <v>Кононов_Иван_Николаевич__Леонтьева_Мария_Петровна</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" t="s">
+        <v>314</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="E6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="str">
+        <f>B7&amp;"__"&amp;C7</f>
+        <v>Кононов_Николай_Спиридонович__Сухарникова_Акулина</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3 B7">
       <formula1>$A:$A</formula1>
     </dataValidation>
   </dataValidations>
@@ -4942,7 +5041,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
@@ -4953,14 +5052,14 @@
         <v>Обозов_Михаил_Никититич__Агафья_Ивановна-.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I2"/>
       <c r="J2" s="2"/>
       <c r="L2"/>
       <c r="M2"/>
       <c r="N2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -5193,7 +5292,7 @@
         <v>242</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G2"/>
       <c r="H2" s="2"/>
@@ -5219,7 +5318,7 @@
         <v>241</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="2"/>
@@ -5358,10 +5457,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
@@ -5371,21 +5470,21 @@
         <v>Луки-Елпатьево-map.png</v>
       </c>
       <c r="E2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="N2"/>
     </row>
@@ -5463,10 +5562,10 @@
     </row>
     <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>280</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>39</v>
@@ -5476,19 +5575,19 @@
         <v>Лебедев_Сергей_Михайлович-учетно_послужная_карточка.jpg</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
